--- a/2_Planning/Cronograma_Seguimiento_ABB.xlsx
+++ b/2_Planning/Cronograma_Seguimiento_ABB.xlsx
@@ -294,12 +294,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DEEAF1"/>
+        <fgColor rgb="007030A0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="007030A0"/>
+        <fgColor rgb="00DEEAF1"/>
       </patternFill>
     </fill>
     <fill>
@@ -507,28 +507,29 @@
     <xf numFmtId="0" fontId="14" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -554,7 +555,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -645,22 +645,22 @@
     <xf numFmtId="0" fontId="25" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -804,19 +804,19 @@
     <xf numFmtId="0" fontId="8" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="25" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1283,7 +1283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX77"/>
+  <dimension ref="A1:CX81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>FAT Maqueta PMS — pruebas funcionales previas</t>
+          <t>FAT Maqueta PMS — Pruebas Tempranas (ET sec.20)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -3787,168 +3787,168 @@
       <c r="CW24" s="14" t="n"/>
       <c r="CX24" s="15" t="n"/>
     </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="31" t="inlineStr">
+    <row r="25" ht="14" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>P-10</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>▶ DESPACHO Tablero PMS — 14-MAY-2027</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>PMS</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>14/05/2027</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>14/05/2027</t>
+        </is>
+      </c>
+      <c r="F25" s="30" t="inlineStr">
+        <is>
+          <t>+222d</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="15" t="n"/>
+      <c r="I25" s="14" t="n"/>
+      <c r="J25" s="15" t="n"/>
+      <c r="K25" s="14" t="n"/>
+      <c r="L25" s="16" t="n"/>
+      <c r="M25" s="14" t="n"/>
+      <c r="N25" s="15" t="n"/>
+      <c r="O25" s="14" t="n"/>
+      <c r="P25" s="16" t="n"/>
+      <c r="Q25" s="14" t="n"/>
+      <c r="R25" s="15" t="n"/>
+      <c r="S25" s="14" t="n"/>
+      <c r="T25" s="15" t="n"/>
+      <c r="U25" s="12" t="n"/>
+      <c r="V25" s="15" t="n"/>
+      <c r="W25" s="14" t="n"/>
+      <c r="X25" s="15" t="n"/>
+      <c r="Y25" s="12" t="n"/>
+      <c r="Z25" s="15" t="n"/>
+      <c r="AA25" s="14" t="n"/>
+      <c r="AB25" s="15" t="n"/>
+      <c r="AC25" s="12" t="n"/>
+      <c r="AD25" s="15" t="n"/>
+      <c r="AE25" s="14" t="n"/>
+      <c r="AF25" s="15" t="n"/>
+      <c r="AG25" s="14" t="n"/>
+      <c r="AH25" s="16" t="n"/>
+      <c r="AI25" s="14" t="n"/>
+      <c r="AJ25" s="15" t="n"/>
+      <c r="AK25" s="14" t="n"/>
+      <c r="AL25" s="16" t="n"/>
+      <c r="AM25" s="14" t="n"/>
+      <c r="AN25" s="15" t="n"/>
+      <c r="AO25" s="14" t="n"/>
+      <c r="AP25" s="16" t="n"/>
+      <c r="AQ25" s="14" t="n"/>
+      <c r="AR25" s="15" t="n"/>
+      <c r="AS25" s="14" t="n"/>
+      <c r="AT25" s="15" t="n"/>
+      <c r="AU25" s="12" t="n"/>
+      <c r="AV25" s="15" t="n"/>
+      <c r="AW25" s="14" t="n"/>
+      <c r="AX25" s="15" t="n"/>
+      <c r="AY25" s="12" t="n"/>
+      <c r="AZ25" s="15" t="n"/>
+      <c r="BA25" s="14" t="n"/>
+      <c r="BB25" s="15" t="n"/>
+      <c r="BC25" s="12" t="n"/>
+      <c r="BD25" s="15" t="n"/>
+      <c r="BE25" s="14" t="n"/>
+      <c r="BF25" s="15" t="n"/>
+      <c r="BG25" s="14" t="n"/>
+      <c r="BH25" s="16" t="n"/>
+      <c r="BI25" s="31" t="n"/>
+      <c r="BJ25" s="15" t="n"/>
+      <c r="BK25" s="14" t="n"/>
+      <c r="BL25" s="16" t="n"/>
+      <c r="BM25" s="14" t="n"/>
+      <c r="BN25" s="15" t="n"/>
+      <c r="BO25" s="14" t="n"/>
+      <c r="BP25" s="16" t="n"/>
+      <c r="BQ25" s="14" t="n"/>
+      <c r="BR25" s="15" t="n"/>
+      <c r="BS25" s="14" t="n"/>
+      <c r="BT25" s="15" t="n"/>
+      <c r="BU25" s="12" t="n"/>
+      <c r="BV25" s="15" t="n"/>
+      <c r="BW25" s="14" t="n"/>
+      <c r="BX25" s="15" t="n"/>
+      <c r="BY25" s="12" t="n"/>
+      <c r="BZ25" s="15" t="n"/>
+      <c r="CA25" s="14" t="n"/>
+      <c r="CB25" s="15" t="n"/>
+      <c r="CC25" s="12" t="n"/>
+      <c r="CD25" s="15" t="n"/>
+      <c r="CE25" s="14" t="n"/>
+      <c r="CF25" s="15" t="n"/>
+      <c r="CG25" s="14" t="n"/>
+      <c r="CH25" s="16" t="n"/>
+      <c r="CI25" s="14" t="n"/>
+      <c r="CJ25" s="15" t="n"/>
+      <c r="CK25" s="14" t="n"/>
+      <c r="CL25" s="16" t="n"/>
+      <c r="CM25" s="14" t="n"/>
+      <c r="CN25" s="15" t="n"/>
+      <c r="CO25" s="14" t="n"/>
+      <c r="CP25" s="15" t="n"/>
+      <c r="CQ25" s="12" t="n"/>
+      <c r="CR25" s="15" t="n"/>
+      <c r="CS25" s="14" t="n"/>
+      <c r="CT25" s="15" t="n"/>
+      <c r="CU25" s="12" t="n"/>
+      <c r="CV25" s="15" t="n"/>
+      <c r="CW25" s="14" t="n"/>
+      <c r="CX25" s="15" t="n"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▶  SALA #4 (MT)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="14" customHeight="1">
-      <c r="A26" s="32" t="inlineStr">
+    <row r="27" ht="14" customHeight="1">
+      <c r="A27" s="33" t="inlineStr">
         <is>
           <t>S4-01</t>
         </is>
       </c>
-      <c r="B26" s="33" t="inlineStr">
+      <c r="B27" s="34" t="inlineStr">
         <is>
           <t>Emisión Ingeniería Básica Sala #4</t>
         </is>
       </c>
-      <c r="C26" s="34" t="inlineStr">
+      <c r="C27" s="35" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="D26" s="34" t="inlineStr">
+      <c r="D27" s="35" t="inlineStr">
         <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="E26" s="34" t="inlineStr">
+      <c r="E27" s="35" t="inlineStr">
         <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="F26" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="15" t="n"/>
-      <c r="I26" s="14" t="n"/>
-      <c r="J26" s="23" t="n"/>
-      <c r="K26" s="23" t="n"/>
-      <c r="L26" s="24" t="n"/>
-      <c r="M26" s="23" t="n"/>
-      <c r="N26" s="15" t="n"/>
-      <c r="O26" s="14" t="n"/>
-      <c r="P26" s="16" t="n"/>
-      <c r="Q26" s="14" t="n"/>
-      <c r="R26" s="15" t="n"/>
-      <c r="S26" s="14" t="n"/>
-      <c r="T26" s="15" t="n"/>
-      <c r="U26" s="12" t="n"/>
-      <c r="V26" s="15" t="n"/>
-      <c r="W26" s="14" t="n"/>
-      <c r="X26" s="15" t="n"/>
-      <c r="Y26" s="12" t="n"/>
-      <c r="Z26" s="15" t="n"/>
-      <c r="AA26" s="14" t="n"/>
-      <c r="AB26" s="15" t="n"/>
-      <c r="AC26" s="12" t="n"/>
-      <c r="AD26" s="15" t="n"/>
-      <c r="AE26" s="14" t="n"/>
-      <c r="AF26" s="15" t="n"/>
-      <c r="AG26" s="14" t="n"/>
-      <c r="AH26" s="16" t="n"/>
-      <c r="AI26" s="14" t="n"/>
-      <c r="AJ26" s="15" t="n"/>
-      <c r="AK26" s="14" t="n"/>
-      <c r="AL26" s="16" t="n"/>
-      <c r="AM26" s="14" t="n"/>
-      <c r="AN26" s="15" t="n"/>
-      <c r="AO26" s="14" t="n"/>
-      <c r="AP26" s="16" t="n"/>
-      <c r="AQ26" s="14" t="n"/>
-      <c r="AR26" s="15" t="n"/>
-      <c r="AS26" s="14" t="n"/>
-      <c r="AT26" s="15" t="n"/>
-      <c r="AU26" s="12" t="n"/>
-      <c r="AV26" s="15" t="n"/>
-      <c r="AW26" s="14" t="n"/>
-      <c r="AX26" s="15" t="n"/>
-      <c r="AY26" s="12" t="n"/>
-      <c r="AZ26" s="15" t="n"/>
-      <c r="BA26" s="14" t="n"/>
-      <c r="BB26" s="15" t="n"/>
-      <c r="BC26" s="12" t="n"/>
-      <c r="BD26" s="15" t="n"/>
-      <c r="BE26" s="14" t="n"/>
-      <c r="BF26" s="15" t="n"/>
-      <c r="BG26" s="14" t="n"/>
-      <c r="BH26" s="16" t="n"/>
-      <c r="BI26" s="14" t="n"/>
-      <c r="BJ26" s="15" t="n"/>
-      <c r="BK26" s="14" t="n"/>
-      <c r="BL26" s="16" t="n"/>
-      <c r="BM26" s="14" t="n"/>
-      <c r="BN26" s="15" t="n"/>
-      <c r="BO26" s="14" t="n"/>
-      <c r="BP26" s="16" t="n"/>
-      <c r="BQ26" s="14" t="n"/>
-      <c r="BR26" s="15" t="n"/>
-      <c r="BS26" s="14" t="n"/>
-      <c r="BT26" s="15" t="n"/>
-      <c r="BU26" s="12" t="n"/>
-      <c r="BV26" s="15" t="n"/>
-      <c r="BW26" s="14" t="n"/>
-      <c r="BX26" s="15" t="n"/>
-      <c r="BY26" s="12" t="n"/>
-      <c r="BZ26" s="15" t="n"/>
-      <c r="CA26" s="14" t="n"/>
-      <c r="CB26" s="15" t="n"/>
-      <c r="CC26" s="12" t="n"/>
-      <c r="CD26" s="15" t="n"/>
-      <c r="CE26" s="14" t="n"/>
-      <c r="CF26" s="15" t="n"/>
-      <c r="CG26" s="14" t="n"/>
-      <c r="CH26" s="16" t="n"/>
-      <c r="CI26" s="14" t="n"/>
-      <c r="CJ26" s="15" t="n"/>
-      <c r="CK26" s="14" t="n"/>
-      <c r="CL26" s="16" t="n"/>
-      <c r="CM26" s="14" t="n"/>
-      <c r="CN26" s="15" t="n"/>
-      <c r="CO26" s="14" t="n"/>
-      <c r="CP26" s="15" t="n"/>
-      <c r="CQ26" s="12" t="n"/>
-      <c r="CR26" s="15" t="n"/>
-      <c r="CS26" s="14" t="n"/>
-      <c r="CT26" s="15" t="n"/>
-      <c r="CU26" s="12" t="n"/>
-      <c r="CV26" s="15" t="n"/>
-      <c r="CW26" s="14" t="n"/>
-      <c r="CX26" s="15" t="n"/>
-    </row>
-    <row r="27" ht="14" customHeight="1">
-      <c r="A27" s="32" t="inlineStr">
-        <is>
-          <t>S4-02</t>
-        </is>
-      </c>
-      <c r="B27" s="33" t="inlineStr">
-        <is>
-          <t>Aprobación IB Sala #4 (AESA — 10 días hábiles)</t>
-        </is>
-      </c>
-      <c r="C27" s="34" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="D27" s="34" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="E27" s="34" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
-      <c r="F27" s="35" t="inlineStr">
+      <c r="F27" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3956,12 +3956,12 @@
       <c r="G27" s="12" t="n"/>
       <c r="H27" s="15" t="n"/>
       <c r="I27" s="14" t="n"/>
-      <c r="J27" s="15" t="n"/>
-      <c r="K27" s="14" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="J27" s="23" t="n"/>
+      <c r="K27" s="23" t="n"/>
+      <c r="L27" s="24" t="n"/>
       <c r="M27" s="23" t="n"/>
-      <c r="N27" s="23" t="n"/>
-      <c r="O27" s="23" t="n"/>
+      <c r="N27" s="15" t="n"/>
+      <c r="O27" s="14" t="n"/>
       <c r="P27" s="16" t="n"/>
       <c r="Q27" s="14" t="n"/>
       <c r="R27" s="15" t="n"/>
@@ -4050,33 +4050,33 @@
       <c r="CW27" s="14" t="n"/>
       <c r="CX27" s="15" t="n"/>
     </row>
-    <row r="28" ht="13" customHeight="1">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>FP-S4-1</t>
-        </is>
-      </c>
-      <c r="B28" s="36" t="inlineStr">
-        <is>
-          <t>◆ FREEZING POINT — Ing. Básica Sala #4</t>
-        </is>
-      </c>
-      <c r="C28" s="34" t="inlineStr">
+    <row r="28" ht="14" customHeight="1">
+      <c r="A28" s="33" t="inlineStr">
+        <is>
+          <t>S4-02</t>
+        </is>
+      </c>
+      <c r="B28" s="34" t="inlineStr">
+        <is>
+          <t>Aprobación IB Sala #4 (AESA — 10 días hábiles)</t>
+        </is>
+      </c>
+      <c r="C28" s="35" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="D28" s="37" t="inlineStr">
+      <c r="D28" s="35" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="E28" s="35" t="inlineStr">
         <is>
           <t>26/06/2026</t>
         </is>
       </c>
-      <c r="E28" s="37" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
-      <c r="F28" s="35" t="inlineStr">
+      <c r="F28" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4087,13 +4087,9 @@
       <c r="J28" s="15" t="n"/>
       <c r="K28" s="14" t="n"/>
       <c r="L28" s="16" t="n"/>
-      <c r="M28" s="14" t="n"/>
-      <c r="N28" s="15" t="n"/>
-      <c r="O28" s="27" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
+      <c r="M28" s="23" t="n"/>
+      <c r="N28" s="23" t="n"/>
+      <c r="O28" s="23" t="n"/>
       <c r="P28" s="16" t="n"/>
       <c r="Q28" s="14" t="n"/>
       <c r="R28" s="15" t="n"/>
@@ -4182,33 +4178,33 @@
       <c r="CW28" s="14" t="n"/>
       <c r="CX28" s="15" t="n"/>
     </row>
-    <row r="29" ht="14" customHeight="1">
-      <c r="A29" s="32" t="inlineStr">
-        <is>
-          <t>S4-03</t>
-        </is>
-      </c>
-      <c r="B29" s="33" t="inlineStr">
-        <is>
-          <t>OC a 3ros: Celdas MT Turquía (post FP-IB)</t>
-        </is>
-      </c>
-      <c r="C29" s="34" t="inlineStr">
+    <row r="29" ht="13" customHeight="1">
+      <c r="A29" s="33" t="inlineStr">
+        <is>
+          <t>FP-S4-1</t>
+        </is>
+      </c>
+      <c r="B29" s="37" t="inlineStr">
+        <is>
+          <t>◆ FREEZING POINT — Ing. Básica Sala #4</t>
+        </is>
+      </c>
+      <c r="C29" s="35" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="D29" s="34" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="E29" s="34" t="inlineStr">
-        <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
-      <c r="F29" s="35" t="inlineStr">
+      <c r="D29" s="38" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="E29" s="38" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4221,9 +4217,13 @@
       <c r="L29" s="16" t="n"/>
       <c r="M29" s="14" t="n"/>
       <c r="N29" s="15" t="n"/>
-      <c r="O29" s="23" t="n"/>
-      <c r="P29" s="24" t="n"/>
-      <c r="Q29" s="23" t="n"/>
+      <c r="O29" s="27" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="P29" s="16" t="n"/>
+      <c r="Q29" s="14" t="n"/>
       <c r="R29" s="15" t="n"/>
       <c r="S29" s="14" t="n"/>
       <c r="T29" s="15" t="n"/>
@@ -4311,32 +4311,32 @@
       <c r="CX29" s="15" t="n"/>
     </row>
     <row r="30" ht="14" customHeight="1">
-      <c r="A30" s="32" t="inlineStr">
-        <is>
-          <t>S4-04</t>
-        </is>
-      </c>
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>Emisión Ingeniería de Detalle Sala #4</t>
-        </is>
-      </c>
-      <c r="C30" s="34" t="inlineStr">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
+          <t>S4-03</t>
+        </is>
+      </c>
+      <c r="B30" s="34" t="inlineStr">
+        <is>
+          <t>OC a 3ros: Celdas MT Turquía (post FP-IB)</t>
+        </is>
+      </c>
+      <c r="C30" s="35" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="D30" s="34" t="inlineStr">
+      <c r="D30" s="35" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="E30" s="34" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="F30" s="35" t="inlineStr">
+      <c r="E30" s="35" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4352,7 +4352,7 @@
       <c r="O30" s="23" t="n"/>
       <c r="P30" s="24" t="n"/>
       <c r="Q30" s="23" t="n"/>
-      <c r="R30" s="23" t="n"/>
+      <c r="R30" s="15" t="n"/>
       <c r="S30" s="14" t="n"/>
       <c r="T30" s="15" t="n"/>
       <c r="U30" s="12" t="n"/>
@@ -4439,32 +4439,32 @@
       <c r="CX30" s="15" t="n"/>
     </row>
     <row r="31" ht="14" customHeight="1">
-      <c r="A31" s="32" t="inlineStr">
-        <is>
-          <t>S4-05</t>
-        </is>
-      </c>
-      <c r="B31" s="33" t="inlineStr">
-        <is>
-          <t>Aprobación ID Sala #4 (AESA — 10 días hábiles)</t>
-        </is>
-      </c>
-      <c r="C31" s="34" t="inlineStr">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>S4-04</t>
+        </is>
+      </c>
+      <c r="B31" s="34" t="inlineStr">
+        <is>
+          <t>Emisión Ingeniería de Detalle Sala #4</t>
+        </is>
+      </c>
+      <c r="C31" s="35" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="D31" s="34" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="E31" s="34" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="F31" s="35" t="inlineStr">
+      <c r="D31" s="35" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="E31" s="35" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4477,14 +4477,14 @@
       <c r="L31" s="16" t="n"/>
       <c r="M31" s="14" t="n"/>
       <c r="N31" s="15" t="n"/>
-      <c r="O31" s="14" t="n"/>
-      <c r="P31" s="16" t="n"/>
-      <c r="Q31" s="14" t="n"/>
+      <c r="O31" s="23" t="n"/>
+      <c r="P31" s="24" t="n"/>
+      <c r="Q31" s="23" t="n"/>
       <c r="R31" s="23" t="n"/>
-      <c r="S31" s="23" t="n"/>
-      <c r="T31" s="23" t="n"/>
-      <c r="U31" s="24" t="n"/>
-      <c r="V31" s="23" t="n"/>
+      <c r="S31" s="14" t="n"/>
+      <c r="T31" s="15" t="n"/>
+      <c r="U31" s="12" t="n"/>
+      <c r="V31" s="15" t="n"/>
       <c r="W31" s="14" t="n"/>
       <c r="X31" s="15" t="n"/>
       <c r="Y31" s="12" t="n"/>
@@ -4566,33 +4566,33 @@
       <c r="CW31" s="14" t="n"/>
       <c r="CX31" s="15" t="n"/>
     </row>
-    <row r="32" ht="13" customHeight="1">
-      <c r="A32" s="32" t="inlineStr">
-        <is>
-          <t>FP-S4-2</t>
-        </is>
-      </c>
-      <c r="B32" s="36" t="inlineStr">
-        <is>
-          <t>◆ FREEZING POINT — Ing. Detalle Sala #4</t>
-        </is>
-      </c>
-      <c r="C32" s="34" t="inlineStr">
+    <row r="32" ht="14" customHeight="1">
+      <c r="A32" s="33" t="inlineStr">
+        <is>
+          <t>S4-05</t>
+        </is>
+      </c>
+      <c r="B32" s="34" t="inlineStr">
+        <is>
+          <t>Aprobación ID Sala #4 (AESA — 10 días hábiles)</t>
+        </is>
+      </c>
+      <c r="C32" s="35" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="D32" s="37" t="inlineStr">
+      <c r="D32" s="35" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E32" s="35" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="E32" s="37" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="F32" s="35" t="inlineStr">
+      <c r="F32" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4608,15 +4608,11 @@
       <c r="O32" s="14" t="n"/>
       <c r="P32" s="16" t="n"/>
       <c r="Q32" s="14" t="n"/>
-      <c r="R32" s="15" t="n"/>
-      <c r="S32" s="14" t="n"/>
-      <c r="T32" s="15" t="n"/>
-      <c r="U32" s="12" t="n"/>
-      <c r="V32" s="27" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
+      <c r="R32" s="23" t="n"/>
+      <c r="S32" s="23" t="n"/>
+      <c r="T32" s="23" t="n"/>
+      <c r="U32" s="24" t="n"/>
+      <c r="V32" s="23" t="n"/>
       <c r="W32" s="14" t="n"/>
       <c r="X32" s="15" t="n"/>
       <c r="Y32" s="12" t="n"/>
@@ -4698,33 +4694,33 @@
       <c r="CW32" s="14" t="n"/>
       <c r="CX32" s="15" t="n"/>
     </row>
-    <row r="33" ht="14" customHeight="1">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t>S4-06</t>
-        </is>
-      </c>
-      <c r="B33" s="33" t="inlineStr">
-        <is>
-          <t>Emisión Ingeniería Constructiva Sala #4</t>
-        </is>
-      </c>
-      <c r="C33" s="34" t="inlineStr">
+    <row r="33" ht="13" customHeight="1">
+      <c r="A33" s="33" t="inlineStr">
+        <is>
+          <t>FP-S4-2</t>
+        </is>
+      </c>
+      <c r="B33" s="37" t="inlineStr">
+        <is>
+          <t>◆ FREEZING POINT — Ing. Detalle Sala #4</t>
+        </is>
+      </c>
+      <c r="C33" s="35" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="D33" s="34" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="E33" s="34" t="inlineStr">
-        <is>
-          <t>21/08/2026</t>
-        </is>
-      </c>
-      <c r="F33" s="35" t="inlineStr">
+      <c r="D33" s="38" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="38" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4743,9 +4739,13 @@
       <c r="R33" s="15" t="n"/>
       <c r="S33" s="14" t="n"/>
       <c r="T33" s="15" t="n"/>
-      <c r="U33" s="24" t="n"/>
-      <c r="V33" s="23" t="n"/>
-      <c r="W33" s="23" t="n"/>
+      <c r="U33" s="12" t="n"/>
+      <c r="V33" s="27" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="W33" s="14" t="n"/>
       <c r="X33" s="15" t="n"/>
       <c r="Y33" s="12" t="n"/>
       <c r="Z33" s="15" t="n"/>
@@ -4827,32 +4827,32 @@
       <c r="CX33" s="15" t="n"/>
     </row>
     <row r="34" ht="14" customHeight="1">
-      <c r="A34" s="32" t="inlineStr">
-        <is>
-          <t>S4-07</t>
-        </is>
-      </c>
-      <c r="B34" s="33" t="inlineStr">
-        <is>
-          <t>Aprobación IC Sala #4 (AESA — 10 días hábiles)</t>
-        </is>
-      </c>
-      <c r="C34" s="34" t="inlineStr">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>S4-06</t>
+        </is>
+      </c>
+      <c r="B34" s="34" t="inlineStr">
+        <is>
+          <t>Emisión Ingeniería Constructiva Sala #4</t>
+        </is>
+      </c>
+      <c r="C34" s="35" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="D34" s="34" t="inlineStr">
-        <is>
-          <t>24/08/2026</t>
-        </is>
-      </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
-      </c>
-      <c r="F34" s="35" t="inlineStr">
+      <c r="D34" s="35" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E34" s="35" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4871,10 +4871,10 @@
       <c r="R34" s="15" t="n"/>
       <c r="S34" s="14" t="n"/>
       <c r="T34" s="15" t="n"/>
-      <c r="U34" s="12" t="n"/>
-      <c r="V34" s="15" t="n"/>
+      <c r="U34" s="24" t="n"/>
+      <c r="V34" s="23" t="n"/>
       <c r="W34" s="23" t="n"/>
-      <c r="X34" s="23" t="n"/>
+      <c r="X34" s="15" t="n"/>
       <c r="Y34" s="12" t="n"/>
       <c r="Z34" s="15" t="n"/>
       <c r="AA34" s="14" t="n"/>
@@ -4954,33 +4954,33 @@
       <c r="CW34" s="14" t="n"/>
       <c r="CX34" s="15" t="n"/>
     </row>
-    <row r="35" ht="13" customHeight="1">
-      <c r="A35" s="32" t="inlineStr">
-        <is>
-          <t>FP-S4-3</t>
-        </is>
-      </c>
-      <c r="B35" s="36" t="inlineStr">
-        <is>
-          <t>◆ FREEZING POINT — Ing. Constructiva Sala #4  ← CIERRA INGENIERÍA S4</t>
-        </is>
-      </c>
-      <c r="C35" s="34" t="inlineStr">
+    <row r="35" ht="14" customHeight="1">
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>S4-07</t>
+        </is>
+      </c>
+      <c r="B35" s="34" t="inlineStr">
+        <is>
+          <t>Aprobación IC Sala #4 (AESA — 10 días hábiles)</t>
+        </is>
+      </c>
+      <c r="C35" s="35" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="D35" s="37" t="inlineStr">
+      <c r="D35" s="35" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="35" t="inlineStr">
         <is>
           <t>28/08/2026</t>
         </is>
       </c>
-      <c r="E35" s="37" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
-      </c>
-      <c r="F35" s="35" t="inlineStr">
+      <c r="F35" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5001,12 +5001,8 @@
       <c r="T35" s="15" t="n"/>
       <c r="U35" s="12" t="n"/>
       <c r="V35" s="15" t="n"/>
-      <c r="W35" s="14" t="n"/>
-      <c r="X35" s="27" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
+      <c r="W35" s="23" t="n"/>
+      <c r="X35" s="23" t="n"/>
       <c r="Y35" s="12" t="n"/>
       <c r="Z35" s="15" t="n"/>
       <c r="AA35" s="14" t="n"/>
@@ -5086,33 +5082,33 @@
       <c r="CW35" s="14" t="n"/>
       <c r="CX35" s="15" t="n"/>
     </row>
-    <row r="36" ht="14" customHeight="1">
-      <c r="A36" s="32" t="inlineStr">
-        <is>
-          <t>S4-08</t>
-        </is>
-      </c>
-      <c r="B36" s="33" t="inlineStr">
-        <is>
-          <t>OC a 3ros: Variadores MT China (post FP-IC)</t>
-        </is>
-      </c>
-      <c r="C36" s="34" t="inlineStr">
+    <row r="36" ht="13" customHeight="1">
+      <c r="A36" s="33" t="inlineStr">
+        <is>
+          <t>FP-S4-3</t>
+        </is>
+      </c>
+      <c r="B36" s="37" t="inlineStr">
+        <is>
+          <t>◆ FREEZING POINT — Ing. Constructiva Sala #4  ← CIERRA INGENIERÍA S4</t>
+        </is>
+      </c>
+      <c r="C36" s="35" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="D36" s="34" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
-        </is>
-      </c>
-      <c r="E36" s="34" t="inlineStr">
-        <is>
-          <t>15/09/2026</t>
-        </is>
-      </c>
-      <c r="F36" s="35" t="inlineStr">
+      <c r="D36" s="38" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="E36" s="38" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5134,9 +5130,13 @@
       <c r="U36" s="12" t="n"/>
       <c r="V36" s="15" t="n"/>
       <c r="W36" s="14" t="n"/>
-      <c r="X36" s="23" t="n"/>
-      <c r="Y36" s="24" t="n"/>
-      <c r="Z36" s="23" t="n"/>
+      <c r="X36" s="27" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="Y36" s="12" t="n"/>
+      <c r="Z36" s="15" t="n"/>
       <c r="AA36" s="14" t="n"/>
       <c r="AB36" s="15" t="n"/>
       <c r="AC36" s="12" t="n"/>
@@ -5215,32 +5215,32 @@
       <c r="CX36" s="15" t="n"/>
     </row>
     <row r="37" ht="14" customHeight="1">
-      <c r="A37" s="32" t="inlineStr">
-        <is>
-          <t>S4-09</t>
-        </is>
-      </c>
-      <c r="B37" s="33" t="inlineStr">
-        <is>
-          <t>Fabricación Tableros S#4 (Brasil — M&amp;B)</t>
-        </is>
-      </c>
-      <c r="C37" s="34" t="inlineStr">
+      <c r="A37" s="33" t="inlineStr">
+        <is>
+          <t>S4-08</t>
+        </is>
+      </c>
+      <c r="B37" s="34" t="inlineStr">
+        <is>
+          <t>OC a 3ros: Variadores MT China (post FP-IC)</t>
+        </is>
+      </c>
+      <c r="C37" s="35" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="D37" s="34" t="inlineStr">
+      <c r="D37" s="35" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="E37" s="34" t="inlineStr">
-        <is>
-          <t>02/11/2026</t>
-        </is>
-      </c>
-      <c r="F37" s="35" t="inlineStr">
+      <c r="E37" s="35" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="F37" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5265,13 +5265,13 @@
       <c r="X37" s="23" t="n"/>
       <c r="Y37" s="24" t="n"/>
       <c r="Z37" s="23" t="n"/>
-      <c r="AA37" s="23" t="n"/>
-      <c r="AB37" s="23" t="n"/>
-      <c r="AC37" s="24" t="n"/>
-      <c r="AD37" s="23" t="n"/>
-      <c r="AE37" s="23" t="n"/>
-      <c r="AF37" s="23" t="n"/>
-      <c r="AG37" s="23" t="n"/>
+      <c r="AA37" s="14" t="n"/>
+      <c r="AB37" s="15" t="n"/>
+      <c r="AC37" s="12" t="n"/>
+      <c r="AD37" s="15" t="n"/>
+      <c r="AE37" s="14" t="n"/>
+      <c r="AF37" s="15" t="n"/>
+      <c r="AG37" s="14" t="n"/>
       <c r="AH37" s="16" t="n"/>
       <c r="AI37" s="14" t="n"/>
       <c r="AJ37" s="15" t="n"/>
@@ -5343,32 +5343,32 @@
       <c r="CX37" s="15" t="n"/>
     </row>
     <row r="38" ht="14" customHeight="1">
-      <c r="A38" s="32" t="inlineStr">
-        <is>
-          <t>S4-10</t>
-        </is>
-      </c>
-      <c r="B38" s="33" t="inlineStr">
-        <is>
-          <t>Ensayos Celdas y Tableros MT Sala #4</t>
-        </is>
-      </c>
-      <c r="C38" s="34" t="inlineStr">
+      <c r="A38" s="33" t="inlineStr">
+        <is>
+          <t>S4-09</t>
+        </is>
+      </c>
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>Fabricación Tableros S#4 (Brasil — M&amp;B)</t>
+        </is>
+      </c>
+      <c r="C38" s="35" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="D38" s="34" t="inlineStr">
-        <is>
-          <t>03/11/2026</t>
-        </is>
-      </c>
-      <c r="E38" s="34" t="inlineStr">
-        <is>
-          <t>23/11/2026</t>
-        </is>
-      </c>
-      <c r="F38" s="35" t="inlineStr">
+      <c r="D38" s="35" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="E38" s="35" t="inlineStr">
+        <is>
+          <t>02/11/2026</t>
+        </is>
+      </c>
+      <c r="F38" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5390,19 +5390,19 @@
       <c r="U38" s="12" t="n"/>
       <c r="V38" s="15" t="n"/>
       <c r="W38" s="14" t="n"/>
-      <c r="X38" s="15" t="n"/>
-      <c r="Y38" s="12" t="n"/>
-      <c r="Z38" s="15" t="n"/>
-      <c r="AA38" s="14" t="n"/>
-      <c r="AB38" s="15" t="n"/>
-      <c r="AC38" s="12" t="n"/>
-      <c r="AD38" s="15" t="n"/>
-      <c r="AE38" s="14" t="n"/>
-      <c r="AF38" s="15" t="n"/>
-      <c r="AG38" s="28" t="n"/>
-      <c r="AH38" s="29" t="n"/>
-      <c r="AI38" s="28" t="n"/>
-      <c r="AJ38" s="28" t="n"/>
+      <c r="X38" s="23" t="n"/>
+      <c r="Y38" s="24" t="n"/>
+      <c r="Z38" s="23" t="n"/>
+      <c r="AA38" s="23" t="n"/>
+      <c r="AB38" s="23" t="n"/>
+      <c r="AC38" s="24" t="n"/>
+      <c r="AD38" s="23" t="n"/>
+      <c r="AE38" s="23" t="n"/>
+      <c r="AF38" s="23" t="n"/>
+      <c r="AG38" s="23" t="n"/>
+      <c r="AH38" s="16" t="n"/>
+      <c r="AI38" s="14" t="n"/>
+      <c r="AJ38" s="15" t="n"/>
       <c r="AK38" s="14" t="n"/>
       <c r="AL38" s="16" t="n"/>
       <c r="AM38" s="14" t="n"/>
@@ -5471,32 +5471,32 @@
       <c r="CX38" s="15" t="n"/>
     </row>
     <row r="39" ht="14" customHeight="1">
-      <c r="A39" s="32" t="inlineStr">
-        <is>
-          <t>S4-11</t>
-        </is>
-      </c>
-      <c r="B39" s="33" t="inlineStr">
-        <is>
-          <t>Acopio materiales en Argentina (celdas + VFDs + ductos S#4)</t>
-        </is>
-      </c>
-      <c r="C39" s="34" t="inlineStr">
+      <c r="A39" s="33" t="inlineStr">
+        <is>
+          <t>S4-10</t>
+        </is>
+      </c>
+      <c r="B39" s="34" t="inlineStr">
+        <is>
+          <t>Ensayos Celdas y Tableros MT Sala #4</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="D39" s="34" t="inlineStr">
-        <is>
-          <t>07/12/2026</t>
-        </is>
-      </c>
-      <c r="E39" s="34" t="inlineStr">
-        <is>
-          <t>15/01/2027</t>
-        </is>
-      </c>
-      <c r="F39" s="35" t="inlineStr">
+      <c r="D39" s="35" t="inlineStr">
+        <is>
+          <t>03/11/2026</t>
+        </is>
+      </c>
+      <c r="E39" s="35" t="inlineStr">
+        <is>
+          <t>23/11/2026</t>
+        </is>
+      </c>
+      <c r="F39" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5527,18 +5527,18 @@
       <c r="AD39" s="15" t="n"/>
       <c r="AE39" s="14" t="n"/>
       <c r="AF39" s="15" t="n"/>
-      <c r="AG39" s="14" t="n"/>
-      <c r="AH39" s="16" t="n"/>
-      <c r="AI39" s="14" t="n"/>
-      <c r="AJ39" s="15" t="n"/>
+      <c r="AG39" s="28" t="n"/>
+      <c r="AH39" s="29" t="n"/>
+      <c r="AI39" s="28" t="n"/>
+      <c r="AJ39" s="28" t="n"/>
       <c r="AK39" s="14" t="n"/>
-      <c r="AL39" s="24" t="n"/>
-      <c r="AM39" s="23" t="n"/>
-      <c r="AN39" s="23" t="n"/>
-      <c r="AO39" s="23" t="n"/>
-      <c r="AP39" s="24" t="n"/>
-      <c r="AQ39" s="23" t="n"/>
-      <c r="AR39" s="23" t="n"/>
+      <c r="AL39" s="16" t="n"/>
+      <c r="AM39" s="14" t="n"/>
+      <c r="AN39" s="15" t="n"/>
+      <c r="AO39" s="14" t="n"/>
+      <c r="AP39" s="16" t="n"/>
+      <c r="AQ39" s="14" t="n"/>
+      <c r="AR39" s="15" t="n"/>
       <c r="AS39" s="14" t="n"/>
       <c r="AT39" s="15" t="n"/>
       <c r="AU39" s="12" t="n"/>
@@ -5599,32 +5599,32 @@
       <c r="CX39" s="15" t="n"/>
     </row>
     <row r="40" ht="14" customHeight="1">
-      <c r="A40" s="32" t="inlineStr">
-        <is>
-          <t>S4-12</t>
-        </is>
-      </c>
-      <c r="B40" s="33" t="inlineStr">
-        <is>
-          <t>Montaje e integración en Shelter S#4 (Bottino — Mendoza)</t>
-        </is>
-      </c>
-      <c r="C40" s="34" t="inlineStr">
+      <c r="A40" s="33" t="inlineStr">
+        <is>
+          <t>S4-11</t>
+        </is>
+      </c>
+      <c r="B40" s="34" t="inlineStr">
+        <is>
+          <t>Acopio materiales en Argentina (celdas + VFDs + ductos S#4)</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="D40" s="34" t="inlineStr">
-        <is>
-          <t>18/01/2027</t>
-        </is>
-      </c>
-      <c r="E40" s="34" t="inlineStr">
-        <is>
-          <t>05/03/2027</t>
-        </is>
-      </c>
-      <c r="F40" s="35" t="inlineStr">
+      <c r="D40" s="35" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+      <c r="E40" s="35" t="inlineStr">
+        <is>
+          <t>15/01/2027</t>
+        </is>
+      </c>
+      <c r="F40" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5660,20 +5660,20 @@
       <c r="AI40" s="14" t="n"/>
       <c r="AJ40" s="15" t="n"/>
       <c r="AK40" s="14" t="n"/>
-      <c r="AL40" s="16" t="n"/>
-      <c r="AM40" s="14" t="n"/>
-      <c r="AN40" s="15" t="n"/>
-      <c r="AO40" s="14" t="n"/>
-      <c r="AP40" s="16" t="n"/>
-      <c r="AQ40" s="14" t="n"/>
+      <c r="AL40" s="24" t="n"/>
+      <c r="AM40" s="23" t="n"/>
+      <c r="AN40" s="23" t="n"/>
+      <c r="AO40" s="23" t="n"/>
+      <c r="AP40" s="24" t="n"/>
+      <c r="AQ40" s="23" t="n"/>
       <c r="AR40" s="23" t="n"/>
-      <c r="AS40" s="23" t="n"/>
-      <c r="AT40" s="23" t="n"/>
-      <c r="AU40" s="24" t="n"/>
-      <c r="AV40" s="23" t="n"/>
-      <c r="AW40" s="23" t="n"/>
-      <c r="AX40" s="23" t="n"/>
-      <c r="AY40" s="24" t="n"/>
+      <c r="AS40" s="14" t="n"/>
+      <c r="AT40" s="15" t="n"/>
+      <c r="AU40" s="12" t="n"/>
+      <c r="AV40" s="15" t="n"/>
+      <c r="AW40" s="14" t="n"/>
+      <c r="AX40" s="15" t="n"/>
+      <c r="AY40" s="12" t="n"/>
       <c r="AZ40" s="15" t="n"/>
       <c r="BA40" s="14" t="n"/>
       <c r="BB40" s="15" t="n"/>
@@ -5727,32 +5727,32 @@
       <c r="CX40" s="15" t="n"/>
     </row>
     <row r="41" ht="14" customHeight="1">
-      <c r="A41" s="32" t="inlineStr">
-        <is>
-          <t>S4-13</t>
-        </is>
-      </c>
-      <c r="B41" s="33" t="inlineStr">
-        <is>
-          <t>FAT Sala Eléctrica #4 (Shelter completo)</t>
-        </is>
-      </c>
-      <c r="C41" s="34" t="inlineStr">
+      <c r="A41" s="33" t="inlineStr">
+        <is>
+          <t>S4-12</t>
+        </is>
+      </c>
+      <c r="B41" s="34" t="inlineStr">
+        <is>
+          <t>Montaje e integración en Shelter S#4 (Bottino — Mendoza)</t>
+        </is>
+      </c>
+      <c r="C41" s="35" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="D41" s="34" t="inlineStr">
-        <is>
-          <t>08/03/2027</t>
-        </is>
-      </c>
-      <c r="E41" s="34" t="inlineStr">
-        <is>
-          <t>16/03/2027</t>
-        </is>
-      </c>
-      <c r="F41" s="35" t="inlineStr">
+      <c r="D41" s="35" t="inlineStr">
+        <is>
+          <t>18/01/2027</t>
+        </is>
+      </c>
+      <c r="E41" s="35" t="inlineStr">
+        <is>
+          <t>05/03/2027</t>
+        </is>
+      </c>
+      <c r="F41" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5794,15 +5794,15 @@
       <c r="AO41" s="14" t="n"/>
       <c r="AP41" s="16" t="n"/>
       <c r="AQ41" s="14" t="n"/>
-      <c r="AR41" s="15" t="n"/>
-      <c r="AS41" s="14" t="n"/>
-      <c r="AT41" s="15" t="n"/>
-      <c r="AU41" s="12" t="n"/>
-      <c r="AV41" s="15" t="n"/>
-      <c r="AW41" s="14" t="n"/>
-      <c r="AX41" s="15" t="n"/>
-      <c r="AY41" s="29" t="n"/>
-      <c r="AZ41" s="28" t="n"/>
+      <c r="AR41" s="23" t="n"/>
+      <c r="AS41" s="23" t="n"/>
+      <c r="AT41" s="23" t="n"/>
+      <c r="AU41" s="24" t="n"/>
+      <c r="AV41" s="23" t="n"/>
+      <c r="AW41" s="23" t="n"/>
+      <c r="AX41" s="23" t="n"/>
+      <c r="AY41" s="24" t="n"/>
+      <c r="AZ41" s="15" t="n"/>
       <c r="BA41" s="14" t="n"/>
       <c r="BB41" s="15" t="n"/>
       <c r="BC41" s="12" t="n"/>
@@ -5855,34 +5855,34 @@
       <c r="CX41" s="15" t="n"/>
     </row>
     <row r="42" ht="14" customHeight="1">
-      <c r="A42" s="32" t="inlineStr">
-        <is>
-          <t>S4-14</t>
-        </is>
-      </c>
-      <c r="B42" s="33" t="inlineStr">
-        <is>
-          <t>▶ DESPACHO Sala #4 → Vaca Muerta</t>
-        </is>
-      </c>
-      <c r="C42" s="34" t="inlineStr">
+      <c r="A42" s="33" t="inlineStr">
+        <is>
+          <t>S4-13</t>
+        </is>
+      </c>
+      <c r="B42" s="34" t="inlineStr">
+        <is>
+          <t>FAT Sala Eléctrica #4 (Shelter completo)</t>
+        </is>
+      </c>
+      <c r="C42" s="35" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="D42" s="34" t="inlineStr">
-        <is>
-          <t>02/04/2027</t>
-        </is>
-      </c>
-      <c r="E42" s="34" t="inlineStr">
-        <is>
-          <t>08/04/2027</t>
-        </is>
-      </c>
-      <c r="F42" s="30" t="inlineStr">
-        <is>
-          <t>+81d</t>
+      <c r="D42" s="35" t="inlineStr">
+        <is>
+          <t>08/03/2027</t>
+        </is>
+      </c>
+      <c r="E42" s="35" t="inlineStr">
+        <is>
+          <t>16/03/2027</t>
+        </is>
+      </c>
+      <c r="F42" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="12" t="n"/>
@@ -5929,11 +5929,11 @@
       <c r="AV42" s="15" t="n"/>
       <c r="AW42" s="14" t="n"/>
       <c r="AX42" s="15" t="n"/>
-      <c r="AY42" s="12" t="n"/>
-      <c r="AZ42" s="15" t="n"/>
+      <c r="AY42" s="29" t="n"/>
+      <c r="AZ42" s="28" t="n"/>
       <c r="BA42" s="14" t="n"/>
       <c r="BB42" s="15" t="n"/>
-      <c r="BC42" s="38" t="n"/>
+      <c r="BC42" s="12" t="n"/>
       <c r="BD42" s="15" t="n"/>
       <c r="BE42" s="14" t="n"/>
       <c r="BF42" s="15" t="n"/>
@@ -5982,28 +5982,28 @@
       <c r="CW42" s="14" t="n"/>
       <c r="CX42" s="15" t="n"/>
     </row>
-    <row r="43" ht="13" customHeight="1">
-      <c r="A43" s="32" t="inlineStr">
-        <is>
-          <t>S4-15</t>
-        </is>
-      </c>
-      <c r="B43" s="36" t="inlineStr">
-        <is>
-          <t>★ ENTREGA S#4 — Cumplimiento OC 4508944973</t>
-        </is>
-      </c>
-      <c r="C43" s="34" t="inlineStr">
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="33" t="inlineStr">
+        <is>
+          <t>S4-14</t>
+        </is>
+      </c>
+      <c r="B43" s="34" t="inlineStr">
+        <is>
+          <t>▶ DESPACHO Sala #4 → Vaca Muerta</t>
+        </is>
+      </c>
+      <c r="C43" s="35" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="D43" s="37" t="inlineStr">
-        <is>
-          <t>08/04/2027</t>
-        </is>
-      </c>
-      <c r="E43" s="37" t="inlineStr">
+      <c r="D43" s="35" t="inlineStr">
+        <is>
+          <t>02/04/2027</t>
+        </is>
+      </c>
+      <c r="E43" s="35" t="inlineStr">
         <is>
           <t>08/04/2027</t>
         </is>
@@ -6061,11 +6061,7 @@
       <c r="AZ43" s="15" t="n"/>
       <c r="BA43" s="14" t="n"/>
       <c r="BB43" s="15" t="n"/>
-      <c r="BC43" s="17" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+      <c r="BC43" s="39" t="n"/>
       <c r="BD43" s="15" t="n"/>
       <c r="BE43" s="14" t="n"/>
       <c r="BF43" s="15" t="n"/>
@@ -6114,168 +6110,172 @@
       <c r="CW43" s="14" t="n"/>
       <c r="CX43" s="15" t="n"/>
     </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="39" t="inlineStr">
+    <row r="44" ht="13" customHeight="1">
+      <c r="A44" s="33" t="inlineStr">
+        <is>
+          <t>S4-15</t>
+        </is>
+      </c>
+      <c r="B44" s="37" t="inlineStr">
+        <is>
+          <t>★ ENTREGA S#4 — Cumplimiento OC 4508944973</t>
+        </is>
+      </c>
+      <c r="C44" s="35" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="D44" s="38" t="inlineStr">
+        <is>
+          <t>08/04/2027</t>
+        </is>
+      </c>
+      <c r="E44" s="38" t="inlineStr">
+        <is>
+          <t>08/04/2027</t>
+        </is>
+      </c>
+      <c r="F44" s="30" t="inlineStr">
+        <is>
+          <t>+81d</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="n"/>
+      <c r="H44" s="15" t="n"/>
+      <c r="I44" s="14" t="n"/>
+      <c r="J44" s="15" t="n"/>
+      <c r="K44" s="14" t="n"/>
+      <c r="L44" s="16" t="n"/>
+      <c r="M44" s="14" t="n"/>
+      <c r="N44" s="15" t="n"/>
+      <c r="O44" s="14" t="n"/>
+      <c r="P44" s="16" t="n"/>
+      <c r="Q44" s="14" t="n"/>
+      <c r="R44" s="15" t="n"/>
+      <c r="S44" s="14" t="n"/>
+      <c r="T44" s="15" t="n"/>
+      <c r="U44" s="12" t="n"/>
+      <c r="V44" s="15" t="n"/>
+      <c r="W44" s="14" t="n"/>
+      <c r="X44" s="15" t="n"/>
+      <c r="Y44" s="12" t="n"/>
+      <c r="Z44" s="15" t="n"/>
+      <c r="AA44" s="14" t="n"/>
+      <c r="AB44" s="15" t="n"/>
+      <c r="AC44" s="12" t="n"/>
+      <c r="AD44" s="15" t="n"/>
+      <c r="AE44" s="14" t="n"/>
+      <c r="AF44" s="15" t="n"/>
+      <c r="AG44" s="14" t="n"/>
+      <c r="AH44" s="16" t="n"/>
+      <c r="AI44" s="14" t="n"/>
+      <c r="AJ44" s="15" t="n"/>
+      <c r="AK44" s="14" t="n"/>
+      <c r="AL44" s="16" t="n"/>
+      <c r="AM44" s="14" t="n"/>
+      <c r="AN44" s="15" t="n"/>
+      <c r="AO44" s="14" t="n"/>
+      <c r="AP44" s="16" t="n"/>
+      <c r="AQ44" s="14" t="n"/>
+      <c r="AR44" s="15" t="n"/>
+      <c r="AS44" s="14" t="n"/>
+      <c r="AT44" s="15" t="n"/>
+      <c r="AU44" s="12" t="n"/>
+      <c r="AV44" s="15" t="n"/>
+      <c r="AW44" s="14" t="n"/>
+      <c r="AX44" s="15" t="n"/>
+      <c r="AY44" s="12" t="n"/>
+      <c r="AZ44" s="15" t="n"/>
+      <c r="BA44" s="14" t="n"/>
+      <c r="BB44" s="15" t="n"/>
+      <c r="BC44" s="17" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="BD44" s="15" t="n"/>
+      <c r="BE44" s="14" t="n"/>
+      <c r="BF44" s="15" t="n"/>
+      <c r="BG44" s="14" t="n"/>
+      <c r="BH44" s="16" t="n"/>
+      <c r="BI44" s="14" t="n"/>
+      <c r="BJ44" s="15" t="n"/>
+      <c r="BK44" s="14" t="n"/>
+      <c r="BL44" s="16" t="n"/>
+      <c r="BM44" s="14" t="n"/>
+      <c r="BN44" s="15" t="n"/>
+      <c r="BO44" s="14" t="n"/>
+      <c r="BP44" s="16" t="n"/>
+      <c r="BQ44" s="14" t="n"/>
+      <c r="BR44" s="15" t="n"/>
+      <c r="BS44" s="14" t="n"/>
+      <c r="BT44" s="15" t="n"/>
+      <c r="BU44" s="12" t="n"/>
+      <c r="BV44" s="15" t="n"/>
+      <c r="BW44" s="14" t="n"/>
+      <c r="BX44" s="15" t="n"/>
+      <c r="BY44" s="12" t="n"/>
+      <c r="BZ44" s="15" t="n"/>
+      <c r="CA44" s="14" t="n"/>
+      <c r="CB44" s="15" t="n"/>
+      <c r="CC44" s="12" t="n"/>
+      <c r="CD44" s="15" t="n"/>
+      <c r="CE44" s="14" t="n"/>
+      <c r="CF44" s="15" t="n"/>
+      <c r="CG44" s="14" t="n"/>
+      <c r="CH44" s="16" t="n"/>
+      <c r="CI44" s="14" t="n"/>
+      <c r="CJ44" s="15" t="n"/>
+      <c r="CK44" s="14" t="n"/>
+      <c r="CL44" s="16" t="n"/>
+      <c r="CM44" s="14" t="n"/>
+      <c r="CN44" s="15" t="n"/>
+      <c r="CO44" s="14" t="n"/>
+      <c r="CP44" s="15" t="n"/>
+      <c r="CQ44" s="12" t="n"/>
+      <c r="CR44" s="15" t="n"/>
+      <c r="CS44" s="14" t="n"/>
+      <c r="CT44" s="15" t="n"/>
+      <c r="CU44" s="12" t="n"/>
+      <c r="CV44" s="15" t="n"/>
+      <c r="CW44" s="14" t="n"/>
+      <c r="CX44" s="15" t="n"/>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▶  SALA #3 (BT) ★ CRÍTICA   ← CADENA CRÍTICA  |  OC 4508944971  |  12 meses  |  Entrega: 14-MAY-2027</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="14" customHeight="1">
-      <c r="A45" s="40" t="inlineStr">
+    <row r="46" ht="14" customHeight="1">
+      <c r="A46" s="41" t="inlineStr">
         <is>
           <t>S3-01</t>
         </is>
       </c>
-      <c r="B45" s="41" t="inlineStr">
+      <c r="B46" s="42" t="inlineStr">
         <is>
           <t>Emisión Ingeniería Básica Sala #3</t>
         </is>
       </c>
-      <c r="C45" s="42" t="inlineStr">
+      <c r="C46" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D45" s="40" t="inlineStr">
+      <c r="D46" s="41" t="inlineStr">
         <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="E45" s="40" t="inlineStr">
+      <c r="E46" s="41" t="inlineStr">
         <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="F45" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="12" t="n"/>
-      <c r="H45" s="15" t="n"/>
-      <c r="I45" s="14" t="n"/>
-      <c r="J45" s="44" t="n"/>
-      <c r="K45" s="44" t="n"/>
-      <c r="L45" s="45" t="n"/>
-      <c r="M45" s="44" t="n"/>
-      <c r="N45" s="15" t="n"/>
-      <c r="O45" s="14" t="n"/>
-      <c r="P45" s="16" t="n"/>
-      <c r="Q45" s="14" t="n"/>
-      <c r="R45" s="15" t="n"/>
-      <c r="S45" s="14" t="n"/>
-      <c r="T45" s="15" t="n"/>
-      <c r="U45" s="12" t="n"/>
-      <c r="V45" s="15" t="n"/>
-      <c r="W45" s="14" t="n"/>
-      <c r="X45" s="15" t="n"/>
-      <c r="Y45" s="12" t="n"/>
-      <c r="Z45" s="15" t="n"/>
-      <c r="AA45" s="14" t="n"/>
-      <c r="AB45" s="15" t="n"/>
-      <c r="AC45" s="12" t="n"/>
-      <c r="AD45" s="15" t="n"/>
-      <c r="AE45" s="14" t="n"/>
-      <c r="AF45" s="15" t="n"/>
-      <c r="AG45" s="14" t="n"/>
-      <c r="AH45" s="16" t="n"/>
-      <c r="AI45" s="14" t="n"/>
-      <c r="AJ45" s="15" t="n"/>
-      <c r="AK45" s="14" t="n"/>
-      <c r="AL45" s="16" t="n"/>
-      <c r="AM45" s="14" t="n"/>
-      <c r="AN45" s="15" t="n"/>
-      <c r="AO45" s="14" t="n"/>
-      <c r="AP45" s="16" t="n"/>
-      <c r="AQ45" s="14" t="n"/>
-      <c r="AR45" s="15" t="n"/>
-      <c r="AS45" s="14" t="n"/>
-      <c r="AT45" s="15" t="n"/>
-      <c r="AU45" s="12" t="n"/>
-      <c r="AV45" s="15" t="n"/>
-      <c r="AW45" s="14" t="n"/>
-      <c r="AX45" s="15" t="n"/>
-      <c r="AY45" s="12" t="n"/>
-      <c r="AZ45" s="15" t="n"/>
-      <c r="BA45" s="14" t="n"/>
-      <c r="BB45" s="15" t="n"/>
-      <c r="BC45" s="12" t="n"/>
-      <c r="BD45" s="15" t="n"/>
-      <c r="BE45" s="14" t="n"/>
-      <c r="BF45" s="15" t="n"/>
-      <c r="BG45" s="14" t="n"/>
-      <c r="BH45" s="16" t="n"/>
-      <c r="BI45" s="14" t="n"/>
-      <c r="BJ45" s="15" t="n"/>
-      <c r="BK45" s="14" t="n"/>
-      <c r="BL45" s="16" t="n"/>
-      <c r="BM45" s="14" t="n"/>
-      <c r="BN45" s="15" t="n"/>
-      <c r="BO45" s="14" t="n"/>
-      <c r="BP45" s="16" t="n"/>
-      <c r="BQ45" s="14" t="n"/>
-      <c r="BR45" s="15" t="n"/>
-      <c r="BS45" s="14" t="n"/>
-      <c r="BT45" s="15" t="n"/>
-      <c r="BU45" s="12" t="n"/>
-      <c r="BV45" s="15" t="n"/>
-      <c r="BW45" s="14" t="n"/>
-      <c r="BX45" s="15" t="n"/>
-      <c r="BY45" s="12" t="n"/>
-      <c r="BZ45" s="15" t="n"/>
-      <c r="CA45" s="14" t="n"/>
-      <c r="CB45" s="15" t="n"/>
-      <c r="CC45" s="12" t="n"/>
-      <c r="CD45" s="15" t="n"/>
-      <c r="CE45" s="14" t="n"/>
-      <c r="CF45" s="15" t="n"/>
-      <c r="CG45" s="14" t="n"/>
-      <c r="CH45" s="16" t="n"/>
-      <c r="CI45" s="14" t="n"/>
-      <c r="CJ45" s="15" t="n"/>
-      <c r="CK45" s="14" t="n"/>
-      <c r="CL45" s="16" t="n"/>
-      <c r="CM45" s="14" t="n"/>
-      <c r="CN45" s="15" t="n"/>
-      <c r="CO45" s="14" t="n"/>
-      <c r="CP45" s="15" t="n"/>
-      <c r="CQ45" s="12" t="n"/>
-      <c r="CR45" s="15" t="n"/>
-      <c r="CS45" s="14" t="n"/>
-      <c r="CT45" s="15" t="n"/>
-      <c r="CU45" s="12" t="n"/>
-      <c r="CV45" s="15" t="n"/>
-      <c r="CW45" s="14" t="n"/>
-      <c r="CX45" s="15" t="n"/>
-    </row>
-    <row r="46" ht="14" customHeight="1">
-      <c r="A46" s="40" t="inlineStr">
-        <is>
-          <t>S3-02</t>
-        </is>
-      </c>
-      <c r="B46" s="41" t="inlineStr">
-        <is>
-          <t>Aprobación IB Sala #3 (AESA — 10 días hábiles)</t>
-        </is>
-      </c>
-      <c r="C46" s="42" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="D46" s="40" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="E46" s="40" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
-      <c r="F46" s="43" t="inlineStr">
+      <c r="F46" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6283,12 +6283,12 @@
       <c r="G46" s="12" t="n"/>
       <c r="H46" s="15" t="n"/>
       <c r="I46" s="14" t="n"/>
-      <c r="J46" s="15" t="n"/>
-      <c r="K46" s="14" t="n"/>
-      <c r="L46" s="16" t="n"/>
-      <c r="M46" s="44" t="n"/>
-      <c r="N46" s="44" t="n"/>
-      <c r="O46" s="44" t="n"/>
+      <c r="J46" s="45" t="n"/>
+      <c r="K46" s="45" t="n"/>
+      <c r="L46" s="46" t="n"/>
+      <c r="M46" s="45" t="n"/>
+      <c r="N46" s="15" t="n"/>
+      <c r="O46" s="14" t="n"/>
       <c r="P46" s="16" t="n"/>
       <c r="Q46" s="14" t="n"/>
       <c r="R46" s="15" t="n"/>
@@ -6377,33 +6377,33 @@
       <c r="CW46" s="14" t="n"/>
       <c r="CX46" s="15" t="n"/>
     </row>
-    <row r="47" ht="13" customHeight="1">
-      <c r="A47" s="40" t="inlineStr">
-        <is>
-          <t>FP-S3-1</t>
-        </is>
-      </c>
-      <c r="B47" s="41" t="inlineStr">
-        <is>
-          <t>◆ FREEZING POINT — Ing. Básica Sala #3</t>
-        </is>
-      </c>
-      <c r="C47" s="42" t="inlineStr">
+    <row r="47" ht="14" customHeight="1">
+      <c r="A47" s="41" t="inlineStr">
+        <is>
+          <t>S3-02</t>
+        </is>
+      </c>
+      <c r="B47" s="42" t="inlineStr">
+        <is>
+          <t>Aprobación IB Sala #3 (AESA — 10 días hábiles)</t>
+        </is>
+      </c>
+      <c r="C47" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D47" s="40" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="E47" s="40" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="F47" s="43" t="inlineStr">
+      <c r="D47" s="41" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="E47" s="41" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="F47" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6414,14 +6414,10 @@
       <c r="J47" s="15" t="n"/>
       <c r="K47" s="14" t="n"/>
       <c r="L47" s="16" t="n"/>
-      <c r="M47" s="14" t="n"/>
-      <c r="N47" s="15" t="n"/>
-      <c r="O47" s="14" t="n"/>
-      <c r="P47" s="46" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
+      <c r="M47" s="45" t="n"/>
+      <c r="N47" s="45" t="n"/>
+      <c r="O47" s="45" t="n"/>
+      <c r="P47" s="16" t="n"/>
       <c r="Q47" s="14" t="n"/>
       <c r="R47" s="15" t="n"/>
       <c r="S47" s="14" t="n"/>
@@ -6509,33 +6505,33 @@
       <c r="CW47" s="14" t="n"/>
       <c r="CX47" s="15" t="n"/>
     </row>
-    <row r="48" ht="14" customHeight="1">
-      <c r="A48" s="40" t="inlineStr">
-        <is>
-          <t>S3-03</t>
-        </is>
-      </c>
-      <c r="B48" s="41" t="inlineStr">
-        <is>
-          <t>OC a 3ros: Ductos de Barras Turquía (post FP-IB S3)</t>
-        </is>
-      </c>
-      <c r="C48" s="42" t="inlineStr">
+    <row r="48" ht="13" customHeight="1">
+      <c r="A48" s="41" t="inlineStr">
+        <is>
+          <t>FP-S3-1</t>
+        </is>
+      </c>
+      <c r="B48" s="42" t="inlineStr">
+        <is>
+          <t>◆ FREEZING POINT — Ing. Básica Sala #3</t>
+        </is>
+      </c>
+      <c r="C48" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D48" s="40" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="E48" s="40" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="F48" s="43" t="inlineStr">
+      <c r="D48" s="41" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="E48" s="41" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="F48" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6549,9 +6545,13 @@
       <c r="M48" s="14" t="n"/>
       <c r="N48" s="15" t="n"/>
       <c r="O48" s="14" t="n"/>
-      <c r="P48" s="45" t="n"/>
-      <c r="Q48" s="44" t="n"/>
-      <c r="R48" s="44" t="n"/>
+      <c r="P48" s="47" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="Q48" s="14" t="n"/>
+      <c r="R48" s="15" t="n"/>
       <c r="S48" s="14" t="n"/>
       <c r="T48" s="15" t="n"/>
       <c r="U48" s="12" t="n"/>
@@ -6638,32 +6638,32 @@
       <c r="CX48" s="15" t="n"/>
     </row>
     <row r="49" ht="14" customHeight="1">
-      <c r="A49" s="40" t="inlineStr">
-        <is>
-          <t>S3-04</t>
-        </is>
-      </c>
-      <c r="B49" s="41" t="inlineStr">
-        <is>
-          <t>OC a 3ros: Variadores BT Finlandia (post FP-IB S3)</t>
-        </is>
-      </c>
-      <c r="C49" s="42" t="inlineStr">
+      <c r="A49" s="41" t="inlineStr">
+        <is>
+          <t>S3-03</t>
+        </is>
+      </c>
+      <c r="B49" s="42" t="inlineStr">
+        <is>
+          <t>OC a 3ros: Ductos de Barras Turquía (post FP-IB S3)</t>
+        </is>
+      </c>
+      <c r="C49" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D49" s="40" t="inlineStr">
+      <c r="D49" s="41" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="E49" s="40" t="inlineStr">
+      <c r="E49" s="41" t="inlineStr">
         <is>
           <t>17/07/2026</t>
         </is>
       </c>
-      <c r="F49" s="43" t="inlineStr">
+      <c r="F49" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6677,9 +6677,9 @@
       <c r="M49" s="14" t="n"/>
       <c r="N49" s="15" t="n"/>
       <c r="O49" s="14" t="n"/>
-      <c r="P49" s="45" t="n"/>
-      <c r="Q49" s="44" t="n"/>
-      <c r="R49" s="44" t="n"/>
+      <c r="P49" s="46" t="n"/>
+      <c r="Q49" s="45" t="n"/>
+      <c r="R49" s="45" t="n"/>
       <c r="S49" s="14" t="n"/>
       <c r="T49" s="15" t="n"/>
       <c r="U49" s="12" t="n"/>
@@ -6766,32 +6766,32 @@
       <c r="CX49" s="15" t="n"/>
     </row>
     <row r="50" ht="14" customHeight="1">
-      <c r="A50" s="40" t="inlineStr">
-        <is>
-          <t>S3-05</t>
-        </is>
-      </c>
-      <c r="B50" s="41" t="inlineStr">
-        <is>
-          <t>Emisión Ingeniería de Detalle Sala #3</t>
-        </is>
-      </c>
-      <c r="C50" s="42" t="inlineStr">
+      <c r="A50" s="41" t="inlineStr">
+        <is>
+          <t>S3-04</t>
+        </is>
+      </c>
+      <c r="B50" s="42" t="inlineStr">
+        <is>
+          <t>OC a 3ros: Variadores BT Finlandia (post FP-IB S3)</t>
+        </is>
+      </c>
+      <c r="C50" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D50" s="40" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="E50" s="40" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="F50" s="43" t="inlineStr">
+      <c r="D50" s="41" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="E50" s="41" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="F50" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6804,12 +6804,12 @@
       <c r="L50" s="16" t="n"/>
       <c r="M50" s="14" t="n"/>
       <c r="N50" s="15" t="n"/>
-      <c r="O50" s="44" t="n"/>
-      <c r="P50" s="45" t="n"/>
-      <c r="Q50" s="44" t="n"/>
-      <c r="R50" s="44" t="n"/>
-      <c r="S50" s="44" t="n"/>
-      <c r="T50" s="44" t="n"/>
+      <c r="O50" s="14" t="n"/>
+      <c r="P50" s="46" t="n"/>
+      <c r="Q50" s="45" t="n"/>
+      <c r="R50" s="45" t="n"/>
+      <c r="S50" s="14" t="n"/>
+      <c r="T50" s="15" t="n"/>
       <c r="U50" s="12" t="n"/>
       <c r="V50" s="15" t="n"/>
       <c r="W50" s="14" t="n"/>
@@ -6894,32 +6894,32 @@
       <c r="CX50" s="15" t="n"/>
     </row>
     <row r="51" ht="14" customHeight="1">
-      <c r="A51" s="40" t="inlineStr">
-        <is>
-          <t>S3-WARN</t>
-        </is>
-      </c>
-      <c r="B51" s="41" t="inlineStr">
-        <is>
-          <t>⚠ OPEN ISSUE: Confirmar cambio CCM7 (3x22kW → 2x45kW+VFD)</t>
-        </is>
-      </c>
-      <c r="C51" s="42" t="inlineStr">
+      <c r="A51" s="41" t="inlineStr">
+        <is>
+          <t>S3-05</t>
+        </is>
+      </c>
+      <c r="B51" s="42" t="inlineStr">
+        <is>
+          <t>Emisión Ingeniería de Detalle Sala #3</t>
+        </is>
+      </c>
+      <c r="C51" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D51" s="40" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="E51" s="40" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="F51" s="43" t="inlineStr">
+      <c r="D51" s="41" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="E51" s="41" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="F51" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6927,21 +6927,17 @@
       <c r="G51" s="12" t="n"/>
       <c r="H51" s="15" t="n"/>
       <c r="I51" s="14" t="n"/>
-      <c r="J51" s="47" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="K51" s="48" t="n"/>
-      <c r="L51" s="49" t="n"/>
+      <c r="J51" s="15" t="n"/>
+      <c r="K51" s="14" t="n"/>
+      <c r="L51" s="16" t="n"/>
       <c r="M51" s="14" t="n"/>
       <c r="N51" s="15" t="n"/>
-      <c r="O51" s="14" t="n"/>
-      <c r="P51" s="16" t="n"/>
-      <c r="Q51" s="14" t="n"/>
-      <c r="R51" s="15" t="n"/>
-      <c r="S51" s="14" t="n"/>
-      <c r="T51" s="15" t="n"/>
+      <c r="O51" s="45" t="n"/>
+      <c r="P51" s="46" t="n"/>
+      <c r="Q51" s="45" t="n"/>
+      <c r="R51" s="45" t="n"/>
+      <c r="S51" s="45" t="n"/>
+      <c r="T51" s="45" t="n"/>
       <c r="U51" s="12" t="n"/>
       <c r="V51" s="15" t="n"/>
       <c r="W51" s="14" t="n"/>
@@ -7026,32 +7022,32 @@
       <c r="CX51" s="15" t="n"/>
     </row>
     <row r="52" ht="14" customHeight="1">
-      <c r="A52" s="40" t="inlineStr">
-        <is>
-          <t>S3-06</t>
-        </is>
-      </c>
-      <c r="B52" s="41" t="inlineStr">
-        <is>
-          <t>Aprobación ID Sala #3 (AESA — 10 días hábiles)</t>
-        </is>
-      </c>
-      <c r="C52" s="42" t="inlineStr">
+      <c r="A52" s="41" t="inlineStr">
+        <is>
+          <t>S3-WARN</t>
+        </is>
+      </c>
+      <c r="B52" s="42" t="inlineStr">
+        <is>
+          <t>⚠ OPEN ISSUE: Confirmar cambio CCM7 (3x22kW → 2x45kW+VFD)</t>
+        </is>
+      </c>
+      <c r="C52" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D52" s="40" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="E52" s="40" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="F52" s="43" t="inlineStr">
+      <c r="D52" s="41" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="E52" s="41" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7059,9 +7055,13 @@
       <c r="G52" s="12" t="n"/>
       <c r="H52" s="15" t="n"/>
       <c r="I52" s="14" t="n"/>
-      <c r="J52" s="15" t="n"/>
-      <c r="K52" s="14" t="n"/>
-      <c r="L52" s="16" t="n"/>
+      <c r="J52" s="48" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="K52" s="49" t="n"/>
+      <c r="L52" s="50" t="n"/>
       <c r="M52" s="14" t="n"/>
       <c r="N52" s="15" t="n"/>
       <c r="O52" s="14" t="n"/>
@@ -7069,9 +7069,9 @@
       <c r="Q52" s="14" t="n"/>
       <c r="R52" s="15" t="n"/>
       <c r="S52" s="14" t="n"/>
-      <c r="T52" s="44" t="n"/>
-      <c r="U52" s="45" t="n"/>
-      <c r="V52" s="44" t="n"/>
+      <c r="T52" s="15" t="n"/>
+      <c r="U52" s="12" t="n"/>
+      <c r="V52" s="15" t="n"/>
       <c r="W52" s="14" t="n"/>
       <c r="X52" s="15" t="n"/>
       <c r="Y52" s="12" t="n"/>
@@ -7153,33 +7153,33 @@
       <c r="CW52" s="14" t="n"/>
       <c r="CX52" s="15" t="n"/>
     </row>
-    <row r="53" ht="13" customHeight="1">
-      <c r="A53" s="40" t="inlineStr">
-        <is>
-          <t>FP-S3-2</t>
-        </is>
-      </c>
-      <c r="B53" s="41" t="inlineStr">
-        <is>
-          <t>◆ FREEZING POINT — Ing. Detalle Sala #3</t>
-        </is>
-      </c>
-      <c r="C53" s="42" t="inlineStr">
+    <row r="53" ht="14" customHeight="1">
+      <c r="A53" s="41" t="inlineStr">
+        <is>
+          <t>S3-06</t>
+        </is>
+      </c>
+      <c r="B53" s="42" t="inlineStr">
+        <is>
+          <t>Aprobación ID Sala #3 (AESA — 10 días hábiles)</t>
+        </is>
+      </c>
+      <c r="C53" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D53" s="40" t="inlineStr">
+      <c r="D53" s="41" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="E53" s="41" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="E53" s="40" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="F53" s="43" t="inlineStr">
+      <c r="F53" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7197,13 +7197,9 @@
       <c r="Q53" s="14" t="n"/>
       <c r="R53" s="15" t="n"/>
       <c r="S53" s="14" t="n"/>
-      <c r="T53" s="15" t="n"/>
-      <c r="U53" s="12" t="n"/>
-      <c r="V53" s="27" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
+      <c r="T53" s="45" t="n"/>
+      <c r="U53" s="46" t="n"/>
+      <c r="V53" s="45" t="n"/>
       <c r="W53" s="14" t="n"/>
       <c r="X53" s="15" t="n"/>
       <c r="Y53" s="12" t="n"/>
@@ -7285,33 +7281,33 @@
       <c r="CW53" s="14" t="n"/>
       <c r="CX53" s="15" t="n"/>
     </row>
-    <row r="54" ht="14" customHeight="1">
-      <c r="A54" s="40" t="inlineStr">
-        <is>
-          <t>S3-07</t>
-        </is>
-      </c>
-      <c r="B54" s="41" t="inlineStr">
-        <is>
-          <t>Emisión Ingeniería Constructiva Sala #3</t>
-        </is>
-      </c>
-      <c r="C54" s="42" t="inlineStr">
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="41" t="inlineStr">
+        <is>
+          <t>FP-S3-2</t>
+        </is>
+      </c>
+      <c r="B54" s="42" t="inlineStr">
+        <is>
+          <t>◆ FREEZING POINT — Ing. Detalle Sala #3</t>
+        </is>
+      </c>
+      <c r="C54" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D54" s="40" t="inlineStr">
-        <is>
-          <t>17/08/2026</t>
-        </is>
-      </c>
-      <c r="E54" s="40" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
-      </c>
-      <c r="F54" s="43" t="inlineStr">
+      <c r="D54" s="41" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E54" s="41" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7331,9 +7327,13 @@
       <c r="S54" s="14" t="n"/>
       <c r="T54" s="15" t="n"/>
       <c r="U54" s="12" t="n"/>
-      <c r="V54" s="44" t="n"/>
-      <c r="W54" s="44" t="n"/>
-      <c r="X54" s="44" t="n"/>
+      <c r="V54" s="27" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="W54" s="14" t="n"/>
+      <c r="X54" s="15" t="n"/>
       <c r="Y54" s="12" t="n"/>
       <c r="Z54" s="15" t="n"/>
       <c r="AA54" s="14" t="n"/>
@@ -7414,32 +7414,32 @@
       <c r="CX54" s="15" t="n"/>
     </row>
     <row r="55" ht="14" customHeight="1">
-      <c r="A55" s="40" t="inlineStr">
-        <is>
-          <t>S3-08</t>
-        </is>
-      </c>
-      <c r="B55" s="41" t="inlineStr">
-        <is>
-          <t>Aprobación IC Sala #3 (AESA — 10 días hábiles)</t>
-        </is>
-      </c>
-      <c r="C55" s="42" t="inlineStr">
+      <c r="A55" s="41" t="inlineStr">
+        <is>
+          <t>S3-07</t>
+        </is>
+      </c>
+      <c r="B55" s="42" t="inlineStr">
+        <is>
+          <t>Emisión Ingeniería Constructiva Sala #3</t>
+        </is>
+      </c>
+      <c r="C55" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D55" s="40" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
-        </is>
-      </c>
-      <c r="E55" s="40" t="inlineStr">
-        <is>
-          <t>12/09/2026</t>
-        </is>
-      </c>
-      <c r="F55" s="43" t="inlineStr">
+      <c r="D55" s="41" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="E55" s="41" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7459,11 +7459,11 @@
       <c r="S55" s="14" t="n"/>
       <c r="T55" s="15" t="n"/>
       <c r="U55" s="12" t="n"/>
-      <c r="V55" s="15" t="n"/>
-      <c r="W55" s="14" t="n"/>
-      <c r="X55" s="44" t="n"/>
-      <c r="Y55" s="45" t="n"/>
-      <c r="Z55" s="44" t="n"/>
+      <c r="V55" s="45" t="n"/>
+      <c r="W55" s="45" t="n"/>
+      <c r="X55" s="45" t="n"/>
+      <c r="Y55" s="12" t="n"/>
+      <c r="Z55" s="15" t="n"/>
       <c r="AA55" s="14" t="n"/>
       <c r="AB55" s="15" t="n"/>
       <c r="AC55" s="12" t="n"/>
@@ -7541,33 +7541,33 @@
       <c r="CW55" s="14" t="n"/>
       <c r="CX55" s="15" t="n"/>
     </row>
-    <row r="56" ht="13" customHeight="1">
-      <c r="A56" s="40" t="inlineStr">
-        <is>
-          <t>FP-S3-3</t>
-        </is>
-      </c>
-      <c r="B56" s="41" t="inlineStr">
-        <is>
-          <t>◆ FREEZING POINT — Ing. Constructiva Sala #3  ← ÚLTIMO FP ABB</t>
-        </is>
-      </c>
-      <c r="C56" s="42" t="inlineStr">
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="41" t="inlineStr">
+        <is>
+          <t>S3-08</t>
+        </is>
+      </c>
+      <c r="B56" s="42" t="inlineStr">
+        <is>
+          <t>Aprobación IC Sala #3 (AESA — 10 días hábiles)</t>
+        </is>
+      </c>
+      <c r="C56" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D56" s="40" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="E56" s="40" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="F56" s="43" t="inlineStr">
+      <c r="D56" s="41" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="E56" s="41" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="F56" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7589,13 +7589,9 @@
       <c r="U56" s="12" t="n"/>
       <c r="V56" s="15" t="n"/>
       <c r="W56" s="14" t="n"/>
-      <c r="X56" s="27" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
-      <c r="Y56" s="12" t="n"/>
-      <c r="Z56" s="15" t="n"/>
+      <c r="X56" s="45" t="n"/>
+      <c r="Y56" s="46" t="n"/>
+      <c r="Z56" s="45" t="n"/>
       <c r="AA56" s="14" t="n"/>
       <c r="AB56" s="15" t="n"/>
       <c r="AC56" s="12" t="n"/>
@@ -7673,33 +7669,33 @@
       <c r="CW56" s="14" t="n"/>
       <c r="CX56" s="15" t="n"/>
     </row>
-    <row r="57" ht="14" customHeight="1">
-      <c r="A57" s="40" t="inlineStr">
-        <is>
-          <t>S3-09</t>
-        </is>
-      </c>
-      <c r="B57" s="41" t="inlineStr">
-        <is>
-          <t>Fabricación Tableros S#3 (37 CCMs — Brasil M&amp;B)</t>
-        </is>
-      </c>
-      <c r="C57" s="42" t="inlineStr">
+    <row r="57" ht="13" customHeight="1">
+      <c r="A57" s="41" t="inlineStr">
+        <is>
+          <t>FP-S3-3</t>
+        </is>
+      </c>
+      <c r="B57" s="42" t="inlineStr">
+        <is>
+          <t>◆ FREEZING POINT — Ing. Constructiva Sala #3  ← ÚLTIMO FP ABB</t>
+        </is>
+      </c>
+      <c r="C57" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D57" s="40" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="E57" s="40" t="inlineStr">
-        <is>
-          <t>02/11/2026</t>
-        </is>
-      </c>
-      <c r="F57" s="43" t="inlineStr">
+      <c r="D57" s="41" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="E57" s="41" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="F57" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7721,16 +7717,20 @@
       <c r="U57" s="12" t="n"/>
       <c r="V57" s="15" t="n"/>
       <c r="W57" s="14" t="n"/>
-      <c r="X57" s="15" t="n"/>
+      <c r="X57" s="27" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
       <c r="Y57" s="12" t="n"/>
-      <c r="Z57" s="44" t="n"/>
-      <c r="AA57" s="44" t="n"/>
-      <c r="AB57" s="44" t="n"/>
-      <c r="AC57" s="45" t="n"/>
-      <c r="AD57" s="44" t="n"/>
-      <c r="AE57" s="44" t="n"/>
-      <c r="AF57" s="44" t="n"/>
-      <c r="AG57" s="44" t="n"/>
+      <c r="Z57" s="15" t="n"/>
+      <c r="AA57" s="14" t="n"/>
+      <c r="AB57" s="15" t="n"/>
+      <c r="AC57" s="12" t="n"/>
+      <c r="AD57" s="15" t="n"/>
+      <c r="AE57" s="14" t="n"/>
+      <c r="AF57" s="15" t="n"/>
+      <c r="AG57" s="14" t="n"/>
       <c r="AH57" s="16" t="n"/>
       <c r="AI57" s="14" t="n"/>
       <c r="AJ57" s="15" t="n"/>
@@ -7802,32 +7802,32 @@
       <c r="CX57" s="15" t="n"/>
     </row>
     <row r="58" ht="14" customHeight="1">
-      <c r="A58" s="40" t="inlineStr">
-        <is>
-          <t>S3-10</t>
-        </is>
-      </c>
-      <c r="B58" s="41" t="inlineStr">
-        <is>
-          <t>Ensayos Celdas y Tableros BT Sala #3</t>
-        </is>
-      </c>
-      <c r="C58" s="42" t="inlineStr">
+      <c r="A58" s="41" t="inlineStr">
+        <is>
+          <t>S3-09</t>
+        </is>
+      </c>
+      <c r="B58" s="42" t="inlineStr">
+        <is>
+          <t>Fabricación Tableros S#3 (37 CCMs — Brasil M&amp;B)</t>
+        </is>
+      </c>
+      <c r="C58" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D58" s="40" t="inlineStr">
-        <is>
-          <t>03/11/2026</t>
-        </is>
-      </c>
-      <c r="E58" s="40" t="inlineStr">
-        <is>
-          <t>23/11/2026</t>
-        </is>
-      </c>
-      <c r="F58" s="43" t="inlineStr">
+      <c r="D58" s="41" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E58" s="41" t="inlineStr">
+        <is>
+          <t>02/11/2026</t>
+        </is>
+      </c>
+      <c r="F58" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7851,17 +7851,17 @@
       <c r="W58" s="14" t="n"/>
       <c r="X58" s="15" t="n"/>
       <c r="Y58" s="12" t="n"/>
-      <c r="Z58" s="15" t="n"/>
-      <c r="AA58" s="14" t="n"/>
-      <c r="AB58" s="15" t="n"/>
-      <c r="AC58" s="12" t="n"/>
-      <c r="AD58" s="15" t="n"/>
-      <c r="AE58" s="14" t="n"/>
-      <c r="AF58" s="15" t="n"/>
-      <c r="AG58" s="28" t="n"/>
-      <c r="AH58" s="29" t="n"/>
-      <c r="AI58" s="28" t="n"/>
-      <c r="AJ58" s="28" t="n"/>
+      <c r="Z58" s="45" t="n"/>
+      <c r="AA58" s="45" t="n"/>
+      <c r="AB58" s="45" t="n"/>
+      <c r="AC58" s="46" t="n"/>
+      <c r="AD58" s="45" t="n"/>
+      <c r="AE58" s="45" t="n"/>
+      <c r="AF58" s="45" t="n"/>
+      <c r="AG58" s="45" t="n"/>
+      <c r="AH58" s="16" t="n"/>
+      <c r="AI58" s="14" t="n"/>
+      <c r="AJ58" s="15" t="n"/>
       <c r="AK58" s="14" t="n"/>
       <c r="AL58" s="16" t="n"/>
       <c r="AM58" s="14" t="n"/>
@@ -7930,32 +7930,32 @@
       <c r="CX58" s="15" t="n"/>
     </row>
     <row r="59" ht="14" customHeight="1">
-      <c r="A59" s="40" t="inlineStr">
-        <is>
-          <t>S3-11</t>
-        </is>
-      </c>
-      <c r="B59" s="41" t="inlineStr">
-        <is>
-          <t>Acopio materiales en Argentina (celdas + VFDs + ductos S#3)</t>
-        </is>
-      </c>
-      <c r="C59" s="42" t="inlineStr">
+      <c r="A59" s="41" t="inlineStr">
+        <is>
+          <t>S3-10</t>
+        </is>
+      </c>
+      <c r="B59" s="42" t="inlineStr">
+        <is>
+          <t>Ensayos Celdas y Tableros BT Sala #3</t>
+        </is>
+      </c>
+      <c r="C59" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D59" s="40" t="inlineStr">
-        <is>
-          <t>07/12/2026</t>
-        </is>
-      </c>
-      <c r="E59" s="40" t="inlineStr">
-        <is>
-          <t>29/01/2027</t>
-        </is>
-      </c>
-      <c r="F59" s="43" t="inlineStr">
+      <c r="D59" s="41" t="inlineStr">
+        <is>
+          <t>03/11/2026</t>
+        </is>
+      </c>
+      <c r="E59" s="41" t="inlineStr">
+        <is>
+          <t>23/11/2026</t>
+        </is>
+      </c>
+      <c r="F59" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7986,20 +7986,20 @@
       <c r="AD59" s="15" t="n"/>
       <c r="AE59" s="14" t="n"/>
       <c r="AF59" s="15" t="n"/>
-      <c r="AG59" s="14" t="n"/>
-      <c r="AH59" s="16" t="n"/>
-      <c r="AI59" s="14" t="n"/>
-      <c r="AJ59" s="15" t="n"/>
+      <c r="AG59" s="28" t="n"/>
+      <c r="AH59" s="29" t="n"/>
+      <c r="AI59" s="28" t="n"/>
+      <c r="AJ59" s="28" t="n"/>
       <c r="AK59" s="14" t="n"/>
-      <c r="AL59" s="45" t="n"/>
-      <c r="AM59" s="44" t="n"/>
-      <c r="AN59" s="44" t="n"/>
-      <c r="AO59" s="44" t="n"/>
-      <c r="AP59" s="45" t="n"/>
-      <c r="AQ59" s="44" t="n"/>
-      <c r="AR59" s="44" t="n"/>
-      <c r="AS59" s="44" t="n"/>
-      <c r="AT59" s="44" t="n"/>
+      <c r="AL59" s="16" t="n"/>
+      <c r="AM59" s="14" t="n"/>
+      <c r="AN59" s="15" t="n"/>
+      <c r="AO59" s="14" t="n"/>
+      <c r="AP59" s="16" t="n"/>
+      <c r="AQ59" s="14" t="n"/>
+      <c r="AR59" s="15" t="n"/>
+      <c r="AS59" s="14" t="n"/>
+      <c r="AT59" s="15" t="n"/>
       <c r="AU59" s="12" t="n"/>
       <c r="AV59" s="15" t="n"/>
       <c r="AW59" s="14" t="n"/>
@@ -8058,32 +8058,32 @@
       <c r="CX59" s="15" t="n"/>
     </row>
     <row r="60" ht="14" customHeight="1">
-      <c r="A60" s="40" t="inlineStr">
-        <is>
-          <t>S3-12</t>
-        </is>
-      </c>
-      <c r="B60" s="41" t="inlineStr">
-        <is>
-          <t>Montaje e integración en Shelter S#3 (Bottino — Mendoza)</t>
-        </is>
-      </c>
-      <c r="C60" s="42" t="inlineStr">
+      <c r="A60" s="41" t="inlineStr">
+        <is>
+          <t>S3-11</t>
+        </is>
+      </c>
+      <c r="B60" s="42" t="inlineStr">
+        <is>
+          <t>Acopio materiales en Argentina (celdas + VFDs + ductos S#3)</t>
+        </is>
+      </c>
+      <c r="C60" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D60" s="40" t="inlineStr">
-        <is>
-          <t>01/02/2027</t>
-        </is>
-      </c>
-      <c r="E60" s="40" t="inlineStr">
-        <is>
-          <t>26/03/2027</t>
-        </is>
-      </c>
-      <c r="F60" s="43" t="inlineStr">
+      <c r="D60" s="41" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+      <c r="E60" s="41" t="inlineStr">
+        <is>
+          <t>29/01/2027</t>
+        </is>
+      </c>
+      <c r="F60" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8119,23 +8119,23 @@
       <c r="AI60" s="14" t="n"/>
       <c r="AJ60" s="15" t="n"/>
       <c r="AK60" s="14" t="n"/>
-      <c r="AL60" s="16" t="n"/>
-      <c r="AM60" s="14" t="n"/>
-      <c r="AN60" s="15" t="n"/>
-      <c r="AO60" s="14" t="n"/>
-      <c r="AP60" s="16" t="n"/>
-      <c r="AQ60" s="14" t="n"/>
-      <c r="AR60" s="15" t="n"/>
-      <c r="AS60" s="14" t="n"/>
-      <c r="AT60" s="44" t="n"/>
-      <c r="AU60" s="45" t="n"/>
-      <c r="AV60" s="44" t="n"/>
-      <c r="AW60" s="44" t="n"/>
-      <c r="AX60" s="44" t="n"/>
-      <c r="AY60" s="45" t="n"/>
-      <c r="AZ60" s="44" t="n"/>
-      <c r="BA60" s="44" t="n"/>
-      <c r="BB60" s="44" t="n"/>
+      <c r="AL60" s="46" t="n"/>
+      <c r="AM60" s="45" t="n"/>
+      <c r="AN60" s="45" t="n"/>
+      <c r="AO60" s="45" t="n"/>
+      <c r="AP60" s="46" t="n"/>
+      <c r="AQ60" s="45" t="n"/>
+      <c r="AR60" s="45" t="n"/>
+      <c r="AS60" s="45" t="n"/>
+      <c r="AT60" s="45" t="n"/>
+      <c r="AU60" s="12" t="n"/>
+      <c r="AV60" s="15" t="n"/>
+      <c r="AW60" s="14" t="n"/>
+      <c r="AX60" s="15" t="n"/>
+      <c r="AY60" s="12" t="n"/>
+      <c r="AZ60" s="15" t="n"/>
+      <c r="BA60" s="14" t="n"/>
+      <c r="BB60" s="15" t="n"/>
       <c r="BC60" s="12" t="n"/>
       <c r="BD60" s="15" t="n"/>
       <c r="BE60" s="14" t="n"/>
@@ -8186,34 +8186,34 @@
       <c r="CX60" s="15" t="n"/>
     </row>
     <row r="61" ht="14" customHeight="1">
-      <c r="A61" s="40" t="inlineStr">
-        <is>
-          <t>S3-13</t>
-        </is>
-      </c>
-      <c r="B61" s="41" t="inlineStr">
-        <is>
-          <t>FAT Sala Eléctrica #3  ← FAT MÁS TARDÍO DE ABB</t>
-        </is>
-      </c>
-      <c r="C61" s="42" t="inlineStr">
+      <c r="A61" s="41" t="inlineStr">
+        <is>
+          <t>S3-12</t>
+        </is>
+      </c>
+      <c r="B61" s="42" t="inlineStr">
+        <is>
+          <t>Montaje e integración en Shelter S#3 (Bottino — Mendoza)</t>
+        </is>
+      </c>
+      <c r="C61" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D61" s="40" t="inlineStr">
-        <is>
-          <t>02/04/2027</t>
-        </is>
-      </c>
-      <c r="E61" s="40" t="inlineStr">
-        <is>
-          <t>19/04/2027</t>
-        </is>
-      </c>
-      <c r="F61" s="30" t="inlineStr">
-        <is>
-          <t>+35d</t>
+      <c r="D61" s="41" t="inlineStr">
+        <is>
+          <t>01/02/2027</t>
+        </is>
+      </c>
+      <c r="E61" s="41" t="inlineStr">
+        <is>
+          <t>26/03/2027</t>
+        </is>
+      </c>
+      <c r="F61" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G61" s="12" t="n"/>
@@ -8255,18 +8255,18 @@
       <c r="AQ61" s="14" t="n"/>
       <c r="AR61" s="15" t="n"/>
       <c r="AS61" s="14" t="n"/>
-      <c r="AT61" s="15" t="n"/>
-      <c r="AU61" s="12" t="n"/>
-      <c r="AV61" s="15" t="n"/>
-      <c r="AW61" s="14" t="n"/>
-      <c r="AX61" s="15" t="n"/>
-      <c r="AY61" s="12" t="n"/>
-      <c r="AZ61" s="15" t="n"/>
-      <c r="BA61" s="14" t="n"/>
-      <c r="BB61" s="15" t="n"/>
-      <c r="BC61" s="29" t="n"/>
-      <c r="BD61" s="28" t="n"/>
-      <c r="BE61" s="28" t="n"/>
+      <c r="AT61" s="45" t="n"/>
+      <c r="AU61" s="46" t="n"/>
+      <c r="AV61" s="45" t="n"/>
+      <c r="AW61" s="45" t="n"/>
+      <c r="AX61" s="45" t="n"/>
+      <c r="AY61" s="46" t="n"/>
+      <c r="AZ61" s="45" t="n"/>
+      <c r="BA61" s="45" t="n"/>
+      <c r="BB61" s="45" t="n"/>
+      <c r="BC61" s="12" t="n"/>
+      <c r="BD61" s="15" t="n"/>
+      <c r="BE61" s="14" t="n"/>
       <c r="BF61" s="15" t="n"/>
       <c r="BG61" s="14" t="n"/>
       <c r="BH61" s="16" t="n"/>
@@ -8314,34 +8314,34 @@
       <c r="CX61" s="15" t="n"/>
     </row>
     <row r="62" ht="14" customHeight="1">
-      <c r="A62" s="40" t="inlineStr">
-        <is>
-          <t>S3-14</t>
-        </is>
-      </c>
-      <c r="B62" s="41" t="inlineStr">
-        <is>
-          <t>▶ DESPACHO Sala #3 ← DESPACHO MÁS TARDÍO DE ABB</t>
-        </is>
-      </c>
-      <c r="C62" s="42" t="inlineStr">
+      <c r="A62" s="41" t="inlineStr">
+        <is>
+          <t>S3-13</t>
+        </is>
+      </c>
+      <c r="B62" s="42" t="inlineStr">
+        <is>
+          <t>FAT Sala Eléctrica #3  ← FAT MÁS TARDÍO DE ABB</t>
+        </is>
+      </c>
+      <c r="C62" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D62" s="40" t="inlineStr">
-        <is>
-          <t>10/05/2027</t>
-        </is>
-      </c>
-      <c r="E62" s="40" t="inlineStr">
-        <is>
-          <t>14/05/2027</t>
+      <c r="D62" s="41" t="inlineStr">
+        <is>
+          <t>02/04/2027</t>
+        </is>
+      </c>
+      <c r="E62" s="41" t="inlineStr">
+        <is>
+          <t>19/04/2027</t>
         </is>
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>+45d</t>
+          <t>+35d</t>
         </is>
       </c>
       <c r="G62" s="12" t="n"/>
@@ -8392,13 +8392,13 @@
       <c r="AZ62" s="15" t="n"/>
       <c r="BA62" s="14" t="n"/>
       <c r="BB62" s="15" t="n"/>
-      <c r="BC62" s="12" t="n"/>
-      <c r="BD62" s="15" t="n"/>
-      <c r="BE62" s="14" t="n"/>
+      <c r="BC62" s="29" t="n"/>
+      <c r="BD62" s="28" t="n"/>
+      <c r="BE62" s="28" t="n"/>
       <c r="BF62" s="15" t="n"/>
       <c r="BG62" s="14" t="n"/>
-      <c r="BH62" s="38" t="n"/>
-      <c r="BI62" s="50" t="n"/>
+      <c r="BH62" s="16" t="n"/>
+      <c r="BI62" s="14" t="n"/>
       <c r="BJ62" s="15" t="n"/>
       <c r="BK62" s="14" t="n"/>
       <c r="BL62" s="16" t="n"/>
@@ -8441,28 +8441,28 @@
       <c r="CW62" s="14" t="n"/>
       <c r="CX62" s="15" t="n"/>
     </row>
-    <row r="63" ht="13" customHeight="1">
-      <c r="A63" s="40" t="inlineStr">
-        <is>
-          <t>S3-15</t>
-        </is>
-      </c>
-      <c r="B63" s="41" t="inlineStr">
-        <is>
-          <t>★ ENTREGA S#3 — Cumplimiento OC 4508944971</t>
-        </is>
-      </c>
-      <c r="C63" s="42" t="inlineStr">
+    <row r="63" ht="14" customHeight="1">
+      <c r="A63" s="41" t="inlineStr">
+        <is>
+          <t>S3-14</t>
+        </is>
+      </c>
+      <c r="B63" s="42" t="inlineStr">
+        <is>
+          <t>▶ DESPACHO Sala #3 ← DESPACHO MÁS TARDÍO DE ABB</t>
+        </is>
+      </c>
+      <c r="C63" s="43" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="D63" s="40" t="inlineStr">
-        <is>
-          <t>14/05/2027</t>
-        </is>
-      </c>
-      <c r="E63" s="51" t="inlineStr">
+      <c r="D63" s="41" t="inlineStr">
+        <is>
+          <t>10/05/2027</t>
+        </is>
+      </c>
+      <c r="E63" s="41" t="inlineStr">
         <is>
           <t>14/05/2027</t>
         </is>
@@ -8525,12 +8525,8 @@
       <c r="BE63" s="14" t="n"/>
       <c r="BF63" s="15" t="n"/>
       <c r="BG63" s="14" t="n"/>
-      <c r="BH63" s="16" t="n"/>
-      <c r="BI63" s="13" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+      <c r="BH63" s="39" t="n"/>
+      <c r="BI63" s="31" t="n"/>
       <c r="BJ63" s="15" t="n"/>
       <c r="BK63" s="14" t="n"/>
       <c r="BL63" s="16" t="n"/>
@@ -8573,154 +8569,154 @@
       <c r="CW63" s="14" t="n"/>
       <c r="CX63" s="15" t="n"/>
     </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="52" t="inlineStr">
+    <row r="64" ht="13" customHeight="1">
+      <c r="A64" s="41" t="inlineStr">
+        <is>
+          <t>S3-15</t>
+        </is>
+      </c>
+      <c r="B64" s="42" t="inlineStr">
+        <is>
+          <t>★ ENTREGA S#3 — Cumplimiento OC 4508944971</t>
+        </is>
+      </c>
+      <c r="C64" s="43" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="D64" s="41" t="inlineStr">
+        <is>
+          <t>14/05/2027</t>
+        </is>
+      </c>
+      <c r="E64" s="51" t="inlineStr">
+        <is>
+          <t>14/05/2027</t>
+        </is>
+      </c>
+      <c r="F64" s="30" t="inlineStr">
+        <is>
+          <t>+45d</t>
+        </is>
+      </c>
+      <c r="G64" s="12" t="n"/>
+      <c r="H64" s="15" t="n"/>
+      <c r="I64" s="14" t="n"/>
+      <c r="J64" s="15" t="n"/>
+      <c r="K64" s="14" t="n"/>
+      <c r="L64" s="16" t="n"/>
+      <c r="M64" s="14" t="n"/>
+      <c r="N64" s="15" t="n"/>
+      <c r="O64" s="14" t="n"/>
+      <c r="P64" s="16" t="n"/>
+      <c r="Q64" s="14" t="n"/>
+      <c r="R64" s="15" t="n"/>
+      <c r="S64" s="14" t="n"/>
+      <c r="T64" s="15" t="n"/>
+      <c r="U64" s="12" t="n"/>
+      <c r="V64" s="15" t="n"/>
+      <c r="W64" s="14" t="n"/>
+      <c r="X64" s="15" t="n"/>
+      <c r="Y64" s="12" t="n"/>
+      <c r="Z64" s="15" t="n"/>
+      <c r="AA64" s="14" t="n"/>
+      <c r="AB64" s="15" t="n"/>
+      <c r="AC64" s="12" t="n"/>
+      <c r="AD64" s="15" t="n"/>
+      <c r="AE64" s="14" t="n"/>
+      <c r="AF64" s="15" t="n"/>
+      <c r="AG64" s="14" t="n"/>
+      <c r="AH64" s="16" t="n"/>
+      <c r="AI64" s="14" t="n"/>
+      <c r="AJ64" s="15" t="n"/>
+      <c r="AK64" s="14" t="n"/>
+      <c r="AL64" s="16" t="n"/>
+      <c r="AM64" s="14" t="n"/>
+      <c r="AN64" s="15" t="n"/>
+      <c r="AO64" s="14" t="n"/>
+      <c r="AP64" s="16" t="n"/>
+      <c r="AQ64" s="14" t="n"/>
+      <c r="AR64" s="15" t="n"/>
+      <c r="AS64" s="14" t="n"/>
+      <c r="AT64" s="15" t="n"/>
+      <c r="AU64" s="12" t="n"/>
+      <c r="AV64" s="15" t="n"/>
+      <c r="AW64" s="14" t="n"/>
+      <c r="AX64" s="15" t="n"/>
+      <c r="AY64" s="12" t="n"/>
+      <c r="AZ64" s="15" t="n"/>
+      <c r="BA64" s="14" t="n"/>
+      <c r="BB64" s="15" t="n"/>
+      <c r="BC64" s="12" t="n"/>
+      <c r="BD64" s="15" t="n"/>
+      <c r="BE64" s="14" t="n"/>
+      <c r="BF64" s="15" t="n"/>
+      <c r="BG64" s="14" t="n"/>
+      <c r="BH64" s="16" t="n"/>
+      <c r="BI64" s="13" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="BJ64" s="15" t="n"/>
+      <c r="BK64" s="14" t="n"/>
+      <c r="BL64" s="16" t="n"/>
+      <c r="BM64" s="14" t="n"/>
+      <c r="BN64" s="15" t="n"/>
+      <c r="BO64" s="14" t="n"/>
+      <c r="BP64" s="16" t="n"/>
+      <c r="BQ64" s="14" t="n"/>
+      <c r="BR64" s="15" t="n"/>
+      <c r="BS64" s="14" t="n"/>
+      <c r="BT64" s="15" t="n"/>
+      <c r="BU64" s="12" t="n"/>
+      <c r="BV64" s="15" t="n"/>
+      <c r="BW64" s="14" t="n"/>
+      <c r="BX64" s="15" t="n"/>
+      <c r="BY64" s="12" t="n"/>
+      <c r="BZ64" s="15" t="n"/>
+      <c r="CA64" s="14" t="n"/>
+      <c r="CB64" s="15" t="n"/>
+      <c r="CC64" s="12" t="n"/>
+      <c r="CD64" s="15" t="n"/>
+      <c r="CE64" s="14" t="n"/>
+      <c r="CF64" s="15" t="n"/>
+      <c r="CG64" s="14" t="n"/>
+      <c r="CH64" s="16" t="n"/>
+      <c r="CI64" s="14" t="n"/>
+      <c r="CJ64" s="15" t="n"/>
+      <c r="CK64" s="14" t="n"/>
+      <c r="CL64" s="16" t="n"/>
+      <c r="CM64" s="14" t="n"/>
+      <c r="CN64" s="15" t="n"/>
+      <c r="CO64" s="14" t="n"/>
+      <c r="CP64" s="15" t="n"/>
+      <c r="CQ64" s="12" t="n"/>
+      <c r="CR64" s="15" t="n"/>
+      <c r="CS64" s="14" t="n"/>
+      <c r="CT64" s="15" t="n"/>
+      <c r="CU64" s="12" t="n"/>
+      <c r="CV64" s="15" t="n"/>
+      <c r="CW64" s="14" t="n"/>
+      <c r="CX64" s="15" t="n"/>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▶  HITOS DE PAGO</t>
         </is>
       </c>
-    </row>
-    <row r="65" ht="14" customHeight="1">
-      <c r="A65" s="53" t="inlineStr">
-        <is>
-          <t>PAY-01</t>
-        </is>
-      </c>
-      <c r="B65" s="54" t="inlineStr">
-        <is>
-          <t>§ 10% — Envío Ingeniería Básica (S3 + S4 + PMS)</t>
-        </is>
-      </c>
-      <c r="C65" s="55" t="inlineStr">
-        <is>
-          <t>S3+S4+PMS</t>
-        </is>
-      </c>
-      <c r="D65" s="55" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="E65" s="55" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="F65" s="56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G65" s="12" t="n"/>
-      <c r="H65" s="15" t="n"/>
-      <c r="I65" s="14" t="n"/>
-      <c r="J65" s="15" t="n"/>
-      <c r="K65" s="14" t="n"/>
-      <c r="L65" s="16" t="n"/>
-      <c r="M65" s="57" t="inlineStr">
-        <is>
-          <t>§</t>
-        </is>
-      </c>
-      <c r="N65" s="15" t="n"/>
-      <c r="O65" s="14" t="n"/>
-      <c r="P65" s="16" t="n"/>
-      <c r="Q65" s="14" t="n"/>
-      <c r="R65" s="15" t="n"/>
-      <c r="S65" s="14" t="n"/>
-      <c r="T65" s="15" t="n"/>
-      <c r="U65" s="12" t="n"/>
-      <c r="V65" s="15" t="n"/>
-      <c r="W65" s="14" t="n"/>
-      <c r="X65" s="15" t="n"/>
-      <c r="Y65" s="12" t="n"/>
-      <c r="Z65" s="15" t="n"/>
-      <c r="AA65" s="14" t="n"/>
-      <c r="AB65" s="15" t="n"/>
-      <c r="AC65" s="12" t="n"/>
-      <c r="AD65" s="15" t="n"/>
-      <c r="AE65" s="14" t="n"/>
-      <c r="AF65" s="15" t="n"/>
-      <c r="AG65" s="14" t="n"/>
-      <c r="AH65" s="16" t="n"/>
-      <c r="AI65" s="14" t="n"/>
-      <c r="AJ65" s="15" t="n"/>
-      <c r="AK65" s="14" t="n"/>
-      <c r="AL65" s="16" t="n"/>
-      <c r="AM65" s="14" t="n"/>
-      <c r="AN65" s="15" t="n"/>
-      <c r="AO65" s="14" t="n"/>
-      <c r="AP65" s="16" t="n"/>
-      <c r="AQ65" s="14" t="n"/>
-      <c r="AR65" s="15" t="n"/>
-      <c r="AS65" s="14" t="n"/>
-      <c r="AT65" s="15" t="n"/>
-      <c r="AU65" s="12" t="n"/>
-      <c r="AV65" s="15" t="n"/>
-      <c r="AW65" s="14" t="n"/>
-      <c r="AX65" s="15" t="n"/>
-      <c r="AY65" s="12" t="n"/>
-      <c r="AZ65" s="15" t="n"/>
-      <c r="BA65" s="14" t="n"/>
-      <c r="BB65" s="15" t="n"/>
-      <c r="BC65" s="12" t="n"/>
-      <c r="BD65" s="15" t="n"/>
-      <c r="BE65" s="14" t="n"/>
-      <c r="BF65" s="15" t="n"/>
-      <c r="BG65" s="14" t="n"/>
-      <c r="BH65" s="16" t="n"/>
-      <c r="BI65" s="14" t="n"/>
-      <c r="BJ65" s="15" t="n"/>
-      <c r="BK65" s="14" t="n"/>
-      <c r="BL65" s="16" t="n"/>
-      <c r="BM65" s="14" t="n"/>
-      <c r="BN65" s="15" t="n"/>
-      <c r="BO65" s="14" t="n"/>
-      <c r="BP65" s="16" t="n"/>
-      <c r="BQ65" s="14" t="n"/>
-      <c r="BR65" s="15" t="n"/>
-      <c r="BS65" s="14" t="n"/>
-      <c r="BT65" s="15" t="n"/>
-      <c r="BU65" s="12" t="n"/>
-      <c r="BV65" s="15" t="n"/>
-      <c r="BW65" s="14" t="n"/>
-      <c r="BX65" s="15" t="n"/>
-      <c r="BY65" s="12" t="n"/>
-      <c r="BZ65" s="15" t="n"/>
-      <c r="CA65" s="14" t="n"/>
-      <c r="CB65" s="15" t="n"/>
-      <c r="CC65" s="12" t="n"/>
-      <c r="CD65" s="15" t="n"/>
-      <c r="CE65" s="14" t="n"/>
-      <c r="CF65" s="15" t="n"/>
-      <c r="CG65" s="14" t="n"/>
-      <c r="CH65" s="16" t="n"/>
-      <c r="CI65" s="14" t="n"/>
-      <c r="CJ65" s="15" t="n"/>
-      <c r="CK65" s="14" t="n"/>
-      <c r="CL65" s="16" t="n"/>
-      <c r="CM65" s="14" t="n"/>
-      <c r="CN65" s="15" t="n"/>
-      <c r="CO65" s="14" t="n"/>
-      <c r="CP65" s="15" t="n"/>
-      <c r="CQ65" s="12" t="n"/>
-      <c r="CR65" s="15" t="n"/>
-      <c r="CS65" s="14" t="n"/>
-      <c r="CT65" s="15" t="n"/>
-      <c r="CU65" s="12" t="n"/>
-      <c r="CV65" s="15" t="n"/>
-      <c r="CW65" s="14" t="n"/>
-      <c r="CX65" s="15" t="n"/>
     </row>
     <row r="66" ht="14" customHeight="1">
       <c r="A66" s="53" t="inlineStr">
         <is>
-          <t>PAY-02</t>
+          <t>PAY-01</t>
         </is>
       </c>
       <c r="B66" s="54" t="inlineStr">
         <is>
-          <t>§ 10% — Aprobación Ingeniería Básica (AESA aprueba)</t>
+          <t>§ 10% — Envío Ingeniería Básica (S3 + S4 + PMS)</t>
         </is>
       </c>
       <c r="C66" s="55" t="inlineStr">
@@ -8730,12 +8726,12 @@
       </c>
       <c r="D66" s="55" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="E66" s="55" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="F66" s="56" t="inlineStr">
@@ -8749,14 +8745,14 @@
       <c r="J66" s="15" t="n"/>
       <c r="K66" s="14" t="n"/>
       <c r="L66" s="16" t="n"/>
-      <c r="M66" s="14" t="n"/>
+      <c r="M66" s="57" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
       <c r="N66" s="15" t="n"/>
       <c r="O66" s="14" t="n"/>
-      <c r="P66" s="58" t="inlineStr">
-        <is>
-          <t>§</t>
-        </is>
-      </c>
+      <c r="P66" s="16" t="n"/>
       <c r="Q66" s="14" t="n"/>
       <c r="R66" s="15" t="n"/>
       <c r="S66" s="14" t="n"/>
@@ -8847,27 +8843,27 @@
     <row r="67" ht="14" customHeight="1">
       <c r="A67" s="53" t="inlineStr">
         <is>
-          <t>PAY-03</t>
+          <t>PAY-02</t>
         </is>
       </c>
       <c r="B67" s="54" t="inlineStr">
         <is>
-          <t>§ 20% — FAT completado (S3 más tardío: 19-ABR-2027)</t>
+          <t>§ 10% — Aprobación Ingeniería Básica (AESA aprueba)</t>
         </is>
       </c>
       <c r="C67" s="55" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S3+S4+PMS</t>
         </is>
       </c>
       <c r="D67" s="55" t="inlineStr">
         <is>
-          <t>19/04/2027</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="E67" s="55" t="inlineStr">
         <is>
-          <t>19/04/2027</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="F67" s="56" t="inlineStr">
@@ -8884,7 +8880,11 @@
       <c r="M67" s="14" t="n"/>
       <c r="N67" s="15" t="n"/>
       <c r="O67" s="14" t="n"/>
-      <c r="P67" s="16" t="n"/>
+      <c r="P67" s="58" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
       <c r="Q67" s="14" t="n"/>
       <c r="R67" s="15" t="n"/>
       <c r="S67" s="14" t="n"/>
@@ -8925,11 +8925,7 @@
       <c r="BB67" s="15" t="n"/>
       <c r="BC67" s="12" t="n"/>
       <c r="BD67" s="15" t="n"/>
-      <c r="BE67" s="57" t="inlineStr">
-        <is>
-          <t>§</t>
-        </is>
-      </c>
+      <c r="BE67" s="14" t="n"/>
       <c r="BF67" s="15" t="n"/>
       <c r="BG67" s="14" t="n"/>
       <c r="BH67" s="16" t="n"/>
@@ -8979,27 +8975,27 @@
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="53" t="inlineStr">
         <is>
-          <t>PAY-04</t>
+          <t>PAY-03</t>
         </is>
       </c>
       <c r="B68" s="54" t="inlineStr">
         <is>
-          <t>§ 25% — Acopio Materiales Principales en Argentina</t>
+          <t>§ 20% — FAT completado (S3 más tardío: 19-ABR-2027)</t>
         </is>
       </c>
       <c r="C68" s="55" t="inlineStr">
         <is>
-          <t>S3+S4+PMS</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="D68" s="55" t="inlineStr">
         <is>
-          <t>29/01/2027</t>
+          <t>19/04/2027</t>
         </is>
       </c>
       <c r="E68" s="55" t="inlineStr">
         <is>
-          <t>29/01/2027</t>
+          <t>19/04/2027</t>
         </is>
       </c>
       <c r="F68" s="56" t="inlineStr">
@@ -9046,11 +9042,7 @@
       <c r="AQ68" s="14" t="n"/>
       <c r="AR68" s="15" t="n"/>
       <c r="AS68" s="14" t="n"/>
-      <c r="AT68" s="57" t="inlineStr">
-        <is>
-          <t>§</t>
-        </is>
-      </c>
+      <c r="AT68" s="15" t="n"/>
       <c r="AU68" s="12" t="n"/>
       <c r="AV68" s="15" t="n"/>
       <c r="AW68" s="14" t="n"/>
@@ -9061,7 +9053,11 @@
       <c r="BB68" s="15" t="n"/>
       <c r="BC68" s="12" t="n"/>
       <c r="BD68" s="15" t="n"/>
-      <c r="BE68" s="14" t="n"/>
+      <c r="BE68" s="57" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
       <c r="BF68" s="15" t="n"/>
       <c r="BG68" s="14" t="n"/>
       <c r="BH68" s="16" t="n"/>
@@ -9111,12 +9107,12 @@
     <row r="69" ht="14" customHeight="1">
       <c r="A69" s="53" t="inlineStr">
         <is>
-          <t>PAY-05</t>
+          <t>PAY-04</t>
         </is>
       </c>
       <c r="B69" s="54" t="inlineStr">
         <is>
-          <t>§ 30% — Contra Entrega (Shelter listo en Mendoza)</t>
+          <t>§ 25% — Acopio Materiales Principales en Argentina</t>
         </is>
       </c>
       <c r="C69" s="55" t="inlineStr">
@@ -9126,12 +9122,12 @@
       </c>
       <c r="D69" s="55" t="inlineStr">
         <is>
-          <t>14/05/2027</t>
+          <t>29/01/2027</t>
         </is>
       </c>
       <c r="E69" s="55" t="inlineStr">
         <is>
-          <t>14/05/2027</t>
+          <t>29/01/2027</t>
         </is>
       </c>
       <c r="F69" s="56" t="inlineStr">
@@ -9178,7 +9174,11 @@
       <c r="AQ69" s="14" t="n"/>
       <c r="AR69" s="15" t="n"/>
       <c r="AS69" s="14" t="n"/>
-      <c r="AT69" s="15" t="n"/>
+      <c r="AT69" s="57" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
       <c r="AU69" s="12" t="n"/>
       <c r="AV69" s="15" t="n"/>
       <c r="AW69" s="14" t="n"/>
@@ -9193,11 +9193,7 @@
       <c r="BF69" s="15" t="n"/>
       <c r="BG69" s="14" t="n"/>
       <c r="BH69" s="16" t="n"/>
-      <c r="BI69" s="57" t="inlineStr">
-        <is>
-          <t>§</t>
-        </is>
-      </c>
+      <c r="BI69" s="14" t="n"/>
       <c r="BJ69" s="15" t="n"/>
       <c r="BK69" s="14" t="n"/>
       <c r="BL69" s="16" t="n"/>
@@ -9243,12 +9239,12 @@
     <row r="70" ht="14" customHeight="1">
       <c r="A70" s="53" t="inlineStr">
         <is>
-          <t>PAY-06</t>
+          <t>PAY-05</t>
         </is>
       </c>
       <c r="B70" s="54" t="inlineStr">
         <is>
-          <t>§ 5% — Entrega Databook aprobado</t>
+          <t>§ 30% — Contra Entrega (Shelter listo en Mendoza)</t>
         </is>
       </c>
       <c r="C70" s="55" t="inlineStr">
@@ -9258,12 +9254,12 @@
       </c>
       <c r="D70" s="55" t="inlineStr">
         <is>
-          <t>01/07/2027</t>
+          <t>14/05/2027</t>
         </is>
       </c>
       <c r="E70" s="55" t="inlineStr">
         <is>
-          <t>01/07/2027</t>
+          <t>14/05/2027</t>
         </is>
       </c>
       <c r="F70" s="56" t="inlineStr">
@@ -9325,17 +9321,17 @@
       <c r="BF70" s="15" t="n"/>
       <c r="BG70" s="14" t="n"/>
       <c r="BH70" s="16" t="n"/>
-      <c r="BI70" s="14" t="n"/>
+      <c r="BI70" s="57" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
       <c r="BJ70" s="15" t="n"/>
       <c r="BK70" s="14" t="n"/>
       <c r="BL70" s="16" t="n"/>
       <c r="BM70" s="14" t="n"/>
       <c r="BN70" s="15" t="n"/>
-      <c r="BO70" s="57" t="inlineStr">
-        <is>
-          <t>§</t>
-        </is>
-      </c>
+      <c r="BO70" s="14" t="n"/>
       <c r="BP70" s="16" t="n"/>
       <c r="BQ70" s="14" t="n"/>
       <c r="BR70" s="15" t="n"/>
@@ -9372,170 +9368,174 @@
       <c r="CW70" s="14" t="n"/>
       <c r="CX70" s="15" t="n"/>
     </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="59" t="inlineStr">
+    <row r="71" ht="14" customHeight="1">
+      <c r="A71" s="53" t="inlineStr">
+        <is>
+          <t>PAY-06</t>
+        </is>
+      </c>
+      <c r="B71" s="54" t="inlineStr">
+        <is>
+          <t>§ 5% — Entrega Databook aprobado</t>
+        </is>
+      </c>
+      <c r="C71" s="55" t="inlineStr">
+        <is>
+          <t>S3+S4+PMS</t>
+        </is>
+      </c>
+      <c r="D71" s="55" t="inlineStr">
+        <is>
+          <t>01/07/2027</t>
+        </is>
+      </c>
+      <c r="E71" s="55" t="inlineStr">
+        <is>
+          <t>01/07/2027</t>
+        </is>
+      </c>
+      <c r="F71" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="12" t="n"/>
+      <c r="H71" s="15" t="n"/>
+      <c r="I71" s="14" t="n"/>
+      <c r="J71" s="15" t="n"/>
+      <c r="K71" s="14" t="n"/>
+      <c r="L71" s="16" t="n"/>
+      <c r="M71" s="14" t="n"/>
+      <c r="N71" s="15" t="n"/>
+      <c r="O71" s="14" t="n"/>
+      <c r="P71" s="16" t="n"/>
+      <c r="Q71" s="14" t="n"/>
+      <c r="R71" s="15" t="n"/>
+      <c r="S71" s="14" t="n"/>
+      <c r="T71" s="15" t="n"/>
+      <c r="U71" s="12" t="n"/>
+      <c r="V71" s="15" t="n"/>
+      <c r="W71" s="14" t="n"/>
+      <c r="X71" s="15" t="n"/>
+      <c r="Y71" s="12" t="n"/>
+      <c r="Z71" s="15" t="n"/>
+      <c r="AA71" s="14" t="n"/>
+      <c r="AB71" s="15" t="n"/>
+      <c r="AC71" s="12" t="n"/>
+      <c r="AD71" s="15" t="n"/>
+      <c r="AE71" s="14" t="n"/>
+      <c r="AF71" s="15" t="n"/>
+      <c r="AG71" s="14" t="n"/>
+      <c r="AH71" s="16" t="n"/>
+      <c r="AI71" s="14" t="n"/>
+      <c r="AJ71" s="15" t="n"/>
+      <c r="AK71" s="14" t="n"/>
+      <c r="AL71" s="16" t="n"/>
+      <c r="AM71" s="14" t="n"/>
+      <c r="AN71" s="15" t="n"/>
+      <c r="AO71" s="14" t="n"/>
+      <c r="AP71" s="16" t="n"/>
+      <c r="AQ71" s="14" t="n"/>
+      <c r="AR71" s="15" t="n"/>
+      <c r="AS71" s="14" t="n"/>
+      <c r="AT71" s="15" t="n"/>
+      <c r="AU71" s="12" t="n"/>
+      <c r="AV71" s="15" t="n"/>
+      <c r="AW71" s="14" t="n"/>
+      <c r="AX71" s="15" t="n"/>
+      <c r="AY71" s="12" t="n"/>
+      <c r="AZ71" s="15" t="n"/>
+      <c r="BA71" s="14" t="n"/>
+      <c r="BB71" s="15" t="n"/>
+      <c r="BC71" s="12" t="n"/>
+      <c r="BD71" s="15" t="n"/>
+      <c r="BE71" s="14" t="n"/>
+      <c r="BF71" s="15" t="n"/>
+      <c r="BG71" s="14" t="n"/>
+      <c r="BH71" s="16" t="n"/>
+      <c r="BI71" s="14" t="n"/>
+      <c r="BJ71" s="15" t="n"/>
+      <c r="BK71" s="14" t="n"/>
+      <c r="BL71" s="16" t="n"/>
+      <c r="BM71" s="14" t="n"/>
+      <c r="BN71" s="15" t="n"/>
+      <c r="BO71" s="57" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="BP71" s="16" t="n"/>
+      <c r="BQ71" s="14" t="n"/>
+      <c r="BR71" s="15" t="n"/>
+      <c r="BS71" s="14" t="n"/>
+      <c r="BT71" s="15" t="n"/>
+      <c r="BU71" s="12" t="n"/>
+      <c r="BV71" s="15" t="n"/>
+      <c r="BW71" s="14" t="n"/>
+      <c r="BX71" s="15" t="n"/>
+      <c r="BY71" s="12" t="n"/>
+      <c r="BZ71" s="15" t="n"/>
+      <c r="CA71" s="14" t="n"/>
+      <c r="CB71" s="15" t="n"/>
+      <c r="CC71" s="12" t="n"/>
+      <c r="CD71" s="15" t="n"/>
+      <c r="CE71" s="14" t="n"/>
+      <c r="CF71" s="15" t="n"/>
+      <c r="CG71" s="14" t="n"/>
+      <c r="CH71" s="16" t="n"/>
+      <c r="CI71" s="14" t="n"/>
+      <c r="CJ71" s="15" t="n"/>
+      <c r="CK71" s="14" t="n"/>
+      <c r="CL71" s="16" t="n"/>
+      <c r="CM71" s="14" t="n"/>
+      <c r="CN71" s="15" t="n"/>
+      <c r="CO71" s="14" t="n"/>
+      <c r="CP71" s="15" t="n"/>
+      <c r="CQ71" s="12" t="n"/>
+      <c r="CR71" s="15" t="n"/>
+      <c r="CS71" s="14" t="n"/>
+      <c r="CT71" s="15" t="n"/>
+      <c r="CU71" s="12" t="n"/>
+      <c r="CV71" s="15" t="n"/>
+      <c r="CW71" s="14" t="n"/>
+      <c r="CX71" s="15" t="n"/>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▶  INTEGRACIÓN EPC</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="14" customHeight="1">
-      <c r="A72" s="60" t="inlineStr">
+    <row r="73" ht="14" customHeight="1">
+      <c r="A73" s="60" t="inlineStr">
         <is>
           <t>INT-01</t>
         </is>
       </c>
-      <c r="B72" s="61" t="inlineStr">
+      <c r="B73" s="61" t="inlineStr">
         <is>
           <t>Inicio Precomisionado</t>
         </is>
       </c>
-      <c r="C72" s="62" t="inlineStr">
+      <c r="C73" s="62" t="inlineStr">
         <is>
           <t>EPC</t>
         </is>
       </c>
-      <c r="D72" s="62" t="inlineStr">
+      <c r="D73" s="62" t="inlineStr">
         <is>
           <t>03/05/2027</t>
         </is>
       </c>
-      <c r="E72" s="62" t="inlineStr">
+      <c r="E73" s="62" t="inlineStr">
         <is>
           <t>13/01/2028</t>
         </is>
       </c>
-      <c r="F72" s="63" t="inlineStr">
+      <c r="F73" s="63" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="12" t="n"/>
-      <c r="H72" s="15" t="n"/>
-      <c r="I72" s="14" t="n"/>
-      <c r="J72" s="15" t="n"/>
-      <c r="K72" s="14" t="n"/>
-      <c r="L72" s="16" t="n"/>
-      <c r="M72" s="14" t="n"/>
-      <c r="N72" s="15" t="n"/>
-      <c r="O72" s="14" t="n"/>
-      <c r="P72" s="16" t="n"/>
-      <c r="Q72" s="14" t="n"/>
-      <c r="R72" s="15" t="n"/>
-      <c r="S72" s="14" t="n"/>
-      <c r="T72" s="15" t="n"/>
-      <c r="U72" s="12" t="n"/>
-      <c r="V72" s="15" t="n"/>
-      <c r="W72" s="14" t="n"/>
-      <c r="X72" s="15" t="n"/>
-      <c r="Y72" s="12" t="n"/>
-      <c r="Z72" s="15" t="n"/>
-      <c r="AA72" s="14" t="n"/>
-      <c r="AB72" s="15" t="n"/>
-      <c r="AC72" s="12" t="n"/>
-      <c r="AD72" s="15" t="n"/>
-      <c r="AE72" s="14" t="n"/>
-      <c r="AF72" s="15" t="n"/>
-      <c r="AG72" s="14" t="n"/>
-      <c r="AH72" s="16" t="n"/>
-      <c r="AI72" s="14" t="n"/>
-      <c r="AJ72" s="15" t="n"/>
-      <c r="AK72" s="14" t="n"/>
-      <c r="AL72" s="16" t="n"/>
-      <c r="AM72" s="14" t="n"/>
-      <c r="AN72" s="15" t="n"/>
-      <c r="AO72" s="14" t="n"/>
-      <c r="AP72" s="16" t="n"/>
-      <c r="AQ72" s="14" t="n"/>
-      <c r="AR72" s="15" t="n"/>
-      <c r="AS72" s="14" t="n"/>
-      <c r="AT72" s="15" t="n"/>
-      <c r="AU72" s="12" t="n"/>
-      <c r="AV72" s="15" t="n"/>
-      <c r="AW72" s="14" t="n"/>
-      <c r="AX72" s="15" t="n"/>
-      <c r="AY72" s="12" t="n"/>
-      <c r="AZ72" s="15" t="n"/>
-      <c r="BA72" s="14" t="n"/>
-      <c r="BB72" s="15" t="n"/>
-      <c r="BC72" s="12" t="n"/>
-      <c r="BD72" s="15" t="n"/>
-      <c r="BE72" s="14" t="n"/>
-      <c r="BF72" s="15" t="n"/>
-      <c r="BG72" s="64" t="n"/>
-      <c r="BH72" s="65" t="n"/>
-      <c r="BI72" s="64" t="n"/>
-      <c r="BJ72" s="64" t="n"/>
-      <c r="BK72" s="64" t="n"/>
-      <c r="BL72" s="65" t="n"/>
-      <c r="BM72" s="64" t="n"/>
-      <c r="BN72" s="64" t="n"/>
-      <c r="BO72" s="64" t="n"/>
-      <c r="BP72" s="65" t="n"/>
-      <c r="BQ72" s="64" t="n"/>
-      <c r="BR72" s="64" t="n"/>
-      <c r="BS72" s="64" t="n"/>
-      <c r="BT72" s="64" t="n"/>
-      <c r="BU72" s="65" t="n"/>
-      <c r="BV72" s="64" t="n"/>
-      <c r="BW72" s="64" t="n"/>
-      <c r="BX72" s="64" t="n"/>
-      <c r="BY72" s="65" t="n"/>
-      <c r="BZ72" s="64" t="n"/>
-      <c r="CA72" s="64" t="n"/>
-      <c r="CB72" s="64" t="n"/>
-      <c r="CC72" s="65" t="n"/>
-      <c r="CD72" s="64" t="n"/>
-      <c r="CE72" s="64" t="n"/>
-      <c r="CF72" s="64" t="n"/>
-      <c r="CG72" s="64" t="n"/>
-      <c r="CH72" s="65" t="n"/>
-      <c r="CI72" s="64" t="n"/>
-      <c r="CJ72" s="64" t="n"/>
-      <c r="CK72" s="64" t="n"/>
-      <c r="CL72" s="65" t="n"/>
-      <c r="CM72" s="64" t="n"/>
-      <c r="CN72" s="64" t="n"/>
-      <c r="CO72" s="64" t="n"/>
-      <c r="CP72" s="64" t="n"/>
-      <c r="CQ72" s="65" t="n"/>
-      <c r="CR72" s="15" t="n"/>
-      <c r="CS72" s="14" t="n"/>
-      <c r="CT72" s="15" t="n"/>
-      <c r="CU72" s="12" t="n"/>
-      <c r="CV72" s="15" t="n"/>
-      <c r="CW72" s="14" t="n"/>
-      <c r="CX72" s="15" t="n"/>
-    </row>
-    <row r="73" ht="14" customHeight="1">
-      <c r="A73" s="66" t="inlineStr">
-        <is>
-          <t>INT-02</t>
-        </is>
-      </c>
-      <c r="B73" s="67" t="inlineStr">
-        <is>
-          <t>iFAT — Integración Shelters + PMS + INAUCO + HIMA</t>
-        </is>
-      </c>
-      <c r="C73" s="62" t="inlineStr">
-        <is>
-          <t>S3+S4+PMS</t>
-        </is>
-      </c>
-      <c r="D73" s="66" t="inlineStr">
-        <is>
-          <t>25/06/2027</t>
-        </is>
-      </c>
-      <c r="E73" s="66" t="inlineStr">
-        <is>
-          <t>14/07/2027</t>
-        </is>
-      </c>
-      <c r="F73" s="68" t="inlineStr">
-        <is>
-          <t>+3d</t>
         </is>
       </c>
       <c r="G73" s="12" t="n"/>
@@ -9590,43 +9590,43 @@
       <c r="BD73" s="15" t="n"/>
       <c r="BE73" s="14" t="n"/>
       <c r="BF73" s="15" t="n"/>
-      <c r="BG73" s="14" t="n"/>
-      <c r="BH73" s="16" t="n"/>
-      <c r="BI73" s="14" t="n"/>
-      <c r="BJ73" s="15" t="n"/>
-      <c r="BK73" s="14" t="n"/>
-      <c r="BL73" s="16" t="n"/>
-      <c r="BM73" s="14" t="n"/>
-      <c r="BN73" s="15" t="n"/>
-      <c r="BO73" s="28" t="n"/>
-      <c r="BP73" s="29" t="n"/>
-      <c r="BQ73" s="28" t="n"/>
-      <c r="BR73" s="15" t="n"/>
-      <c r="BS73" s="14" t="n"/>
-      <c r="BT73" s="15" t="n"/>
-      <c r="BU73" s="12" t="n"/>
-      <c r="BV73" s="15" t="n"/>
-      <c r="BW73" s="14" t="n"/>
-      <c r="BX73" s="15" t="n"/>
-      <c r="BY73" s="12" t="n"/>
-      <c r="BZ73" s="15" t="n"/>
-      <c r="CA73" s="14" t="n"/>
-      <c r="CB73" s="15" t="n"/>
-      <c r="CC73" s="12" t="n"/>
-      <c r="CD73" s="15" t="n"/>
-      <c r="CE73" s="14" t="n"/>
-      <c r="CF73" s="15" t="n"/>
-      <c r="CG73" s="14" t="n"/>
-      <c r="CH73" s="16" t="n"/>
-      <c r="CI73" s="14" t="n"/>
-      <c r="CJ73" s="15" t="n"/>
-      <c r="CK73" s="14" t="n"/>
-      <c r="CL73" s="16" t="n"/>
-      <c r="CM73" s="14" t="n"/>
-      <c r="CN73" s="15" t="n"/>
-      <c r="CO73" s="14" t="n"/>
-      <c r="CP73" s="15" t="n"/>
-      <c r="CQ73" s="12" t="n"/>
+      <c r="BG73" s="64" t="n"/>
+      <c r="BH73" s="65" t="n"/>
+      <c r="BI73" s="64" t="n"/>
+      <c r="BJ73" s="64" t="n"/>
+      <c r="BK73" s="64" t="n"/>
+      <c r="BL73" s="65" t="n"/>
+      <c r="BM73" s="64" t="n"/>
+      <c r="BN73" s="64" t="n"/>
+      <c r="BO73" s="64" t="n"/>
+      <c r="BP73" s="65" t="n"/>
+      <c r="BQ73" s="64" t="n"/>
+      <c r="BR73" s="64" t="n"/>
+      <c r="BS73" s="64" t="n"/>
+      <c r="BT73" s="64" t="n"/>
+      <c r="BU73" s="65" t="n"/>
+      <c r="BV73" s="64" t="n"/>
+      <c r="BW73" s="64" t="n"/>
+      <c r="BX73" s="64" t="n"/>
+      <c r="BY73" s="65" t="n"/>
+      <c r="BZ73" s="64" t="n"/>
+      <c r="CA73" s="64" t="n"/>
+      <c r="CB73" s="64" t="n"/>
+      <c r="CC73" s="65" t="n"/>
+      <c r="CD73" s="64" t="n"/>
+      <c r="CE73" s="64" t="n"/>
+      <c r="CF73" s="64" t="n"/>
+      <c r="CG73" s="64" t="n"/>
+      <c r="CH73" s="65" t="n"/>
+      <c r="CI73" s="64" t="n"/>
+      <c r="CJ73" s="64" t="n"/>
+      <c r="CK73" s="64" t="n"/>
+      <c r="CL73" s="65" t="n"/>
+      <c r="CM73" s="64" t="n"/>
+      <c r="CN73" s="64" t="n"/>
+      <c r="CO73" s="64" t="n"/>
+      <c r="CP73" s="64" t="n"/>
+      <c r="CQ73" s="65" t="n"/>
       <c r="CR73" s="15" t="n"/>
       <c r="CS73" s="14" t="n"/>
       <c r="CT73" s="15" t="n"/>
@@ -9636,34 +9636,34 @@
       <c r="CX73" s="15" t="n"/>
     </row>
     <row r="74" ht="14" customHeight="1">
-      <c r="A74" s="60" t="inlineStr">
-        <is>
-          <t>INT-03</t>
-        </is>
-      </c>
-      <c r="B74" s="61" t="inlineStr">
-        <is>
-          <t>Inicio montaje Shelters en campo (S#3 y S#4)</t>
+      <c r="A74" s="66" t="inlineStr">
+        <is>
+          <t>INT-02</t>
+        </is>
+      </c>
+      <c r="B74" s="67" t="inlineStr">
+        <is>
+          <t>iFAT — Integración Shelters + PMS + INAUCO + HIMA</t>
         </is>
       </c>
       <c r="C74" s="62" t="inlineStr">
         <is>
-          <t>EPC</t>
-        </is>
-      </c>
-      <c r="D74" s="62" t="inlineStr">
-        <is>
-          <t>28/06/2027</t>
-        </is>
-      </c>
-      <c r="E74" s="62" t="inlineStr">
-        <is>
-          <t>21/08/2027</t>
-        </is>
-      </c>
-      <c r="F74" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>S3+S4+PMS</t>
+        </is>
+      </c>
+      <c r="D74" s="66" t="inlineStr">
+        <is>
+          <t>25/06/2027</t>
+        </is>
+      </c>
+      <c r="E74" s="66" t="inlineStr">
+        <is>
+          <t>14/07/2027</t>
+        </is>
+      </c>
+      <c r="F74" s="68" t="inlineStr">
+        <is>
+          <t>+3d</t>
         </is>
       </c>
       <c r="G74" s="12" t="n"/>
@@ -9726,15 +9726,15 @@
       <c r="BL74" s="16" t="n"/>
       <c r="BM74" s="14" t="n"/>
       <c r="BN74" s="15" t="n"/>
-      <c r="BO74" s="64" t="n"/>
-      <c r="BP74" s="65" t="n"/>
-      <c r="BQ74" s="64" t="n"/>
-      <c r="BR74" s="64" t="n"/>
-      <c r="BS74" s="64" t="n"/>
-      <c r="BT74" s="64" t="n"/>
-      <c r="BU74" s="65" t="n"/>
-      <c r="BV74" s="64" t="n"/>
-      <c r="BW74" s="64" t="n"/>
+      <c r="BO74" s="28" t="n"/>
+      <c r="BP74" s="29" t="n"/>
+      <c r="BQ74" s="28" t="n"/>
+      <c r="BR74" s="15" t="n"/>
+      <c r="BS74" s="14" t="n"/>
+      <c r="BT74" s="15" t="n"/>
+      <c r="BU74" s="12" t="n"/>
+      <c r="BV74" s="15" t="n"/>
+      <c r="BW74" s="14" t="n"/>
       <c r="BX74" s="15" t="n"/>
       <c r="BY74" s="12" t="n"/>
       <c r="BZ74" s="15" t="n"/>
@@ -9764,14 +9764,14 @@
       <c r="CX74" s="15" t="n"/>
     </row>
     <row r="75" ht="14" customHeight="1">
-      <c r="A75" s="66" t="inlineStr">
-        <is>
-          <t>INT-04</t>
-        </is>
-      </c>
-      <c r="B75" s="67" t="inlineStr">
-        <is>
-          <t>Inicio Comisionado</t>
+      <c r="A75" s="60" t="inlineStr">
+        <is>
+          <t>INT-03</t>
+        </is>
+      </c>
+      <c r="B75" s="61" t="inlineStr">
+        <is>
+          <t>Inicio montaje Shelters en campo (S#3 y S#4)</t>
         </is>
       </c>
       <c r="C75" s="62" t="inlineStr">
@@ -9779,14 +9779,14 @@
           <t>EPC</t>
         </is>
       </c>
-      <c r="D75" s="66" t="inlineStr">
-        <is>
-          <t>16/07/2027</t>
-        </is>
-      </c>
-      <c r="E75" s="66" t="inlineStr">
-        <is>
-          <t>31/01/2028</t>
+      <c r="D75" s="62" t="inlineStr">
+        <is>
+          <t>28/06/2027</t>
+        </is>
+      </c>
+      <c r="E75" s="62" t="inlineStr">
+        <is>
+          <t>21/08/2027</t>
         </is>
       </c>
       <c r="F75" s="63" t="inlineStr">
@@ -9854,65 +9854,65 @@
       <c r="BL75" s="16" t="n"/>
       <c r="BM75" s="14" t="n"/>
       <c r="BN75" s="15" t="n"/>
-      <c r="BO75" s="14" t="n"/>
-      <c r="BP75" s="16" t="n"/>
-      <c r="BQ75" s="14" t="n"/>
+      <c r="BO75" s="64" t="n"/>
+      <c r="BP75" s="65" t="n"/>
+      <c r="BQ75" s="64" t="n"/>
       <c r="BR75" s="64" t="n"/>
       <c r="BS75" s="64" t="n"/>
       <c r="BT75" s="64" t="n"/>
       <c r="BU75" s="65" t="n"/>
       <c r="BV75" s="64" t="n"/>
       <c r="BW75" s="64" t="n"/>
-      <c r="BX75" s="64" t="n"/>
-      <c r="BY75" s="65" t="n"/>
-      <c r="BZ75" s="64" t="n"/>
-      <c r="CA75" s="64" t="n"/>
-      <c r="CB75" s="64" t="n"/>
-      <c r="CC75" s="65" t="n"/>
-      <c r="CD75" s="64" t="n"/>
-      <c r="CE75" s="64" t="n"/>
-      <c r="CF75" s="64" t="n"/>
-      <c r="CG75" s="64" t="n"/>
-      <c r="CH75" s="65" t="n"/>
-      <c r="CI75" s="64" t="n"/>
-      <c r="CJ75" s="64" t="n"/>
-      <c r="CK75" s="64" t="n"/>
-      <c r="CL75" s="65" t="n"/>
-      <c r="CM75" s="64" t="n"/>
-      <c r="CN75" s="64" t="n"/>
-      <c r="CO75" s="64" t="n"/>
-      <c r="CP75" s="64" t="n"/>
-      <c r="CQ75" s="65" t="n"/>
-      <c r="CR75" s="64" t="n"/>
-      <c r="CS75" s="64" t="n"/>
-      <c r="CT75" s="64" t="n"/>
+      <c r="BX75" s="15" t="n"/>
+      <c r="BY75" s="12" t="n"/>
+      <c r="BZ75" s="15" t="n"/>
+      <c r="CA75" s="14" t="n"/>
+      <c r="CB75" s="15" t="n"/>
+      <c r="CC75" s="12" t="n"/>
+      <c r="CD75" s="15" t="n"/>
+      <c r="CE75" s="14" t="n"/>
+      <c r="CF75" s="15" t="n"/>
+      <c r="CG75" s="14" t="n"/>
+      <c r="CH75" s="16" t="n"/>
+      <c r="CI75" s="14" t="n"/>
+      <c r="CJ75" s="15" t="n"/>
+      <c r="CK75" s="14" t="n"/>
+      <c r="CL75" s="16" t="n"/>
+      <c r="CM75" s="14" t="n"/>
+      <c r="CN75" s="15" t="n"/>
+      <c r="CO75" s="14" t="n"/>
+      <c r="CP75" s="15" t="n"/>
+      <c r="CQ75" s="12" t="n"/>
+      <c r="CR75" s="15" t="n"/>
+      <c r="CS75" s="14" t="n"/>
+      <c r="CT75" s="15" t="n"/>
       <c r="CU75" s="12" t="n"/>
       <c r="CV75" s="15" t="n"/>
       <c r="CW75" s="14" t="n"/>
       <c r="CX75" s="15" t="n"/>
     </row>
-    <row r="76" ht="13" customHeight="1">
+    <row r="76" ht="14" customHeight="1">
       <c r="A76" s="66" t="inlineStr">
         <is>
-          <t>INT-05</t>
+          <t>INT-04</t>
         </is>
       </c>
       <c r="B76" s="67" t="inlineStr">
         <is>
-          <t>★ RFSU — Ready For Start Up Planta Total</t>
+          <t>Inicio Comisionado</t>
         </is>
       </c>
       <c r="C76" s="62" t="inlineStr">
         <is>
-          <t>PROYECTO</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="D76" s="66" t="inlineStr">
         <is>
-          <t>31/01/2028</t>
-        </is>
-      </c>
-      <c r="E76" s="69" t="inlineStr">
+          <t>16/07/2027</t>
+        </is>
+      </c>
+      <c r="E76" s="66" t="inlineStr">
         <is>
           <t>31/01/2028</t>
         </is>
@@ -9985,46 +9985,558 @@
       <c r="BO76" s="14" t="n"/>
       <c r="BP76" s="16" t="n"/>
       <c r="BQ76" s="14" t="n"/>
-      <c r="BR76" s="15" t="n"/>
-      <c r="BS76" s="14" t="n"/>
-      <c r="BT76" s="15" t="n"/>
-      <c r="BU76" s="12" t="n"/>
-      <c r="BV76" s="15" t="n"/>
-      <c r="BW76" s="14" t="n"/>
-      <c r="BX76" s="15" t="n"/>
-      <c r="BY76" s="12" t="n"/>
-      <c r="BZ76" s="15" t="n"/>
-      <c r="CA76" s="14" t="n"/>
-      <c r="CB76" s="15" t="n"/>
-      <c r="CC76" s="12" t="n"/>
-      <c r="CD76" s="15" t="n"/>
-      <c r="CE76" s="14" t="n"/>
-      <c r="CF76" s="15" t="n"/>
-      <c r="CG76" s="14" t="n"/>
-      <c r="CH76" s="16" t="n"/>
-      <c r="CI76" s="14" t="n"/>
-      <c r="CJ76" s="15" t="n"/>
-      <c r="CK76" s="14" t="n"/>
-      <c r="CL76" s="16" t="n"/>
-      <c r="CM76" s="14" t="n"/>
-      <c r="CN76" s="15" t="n"/>
-      <c r="CO76" s="14" t="n"/>
-      <c r="CP76" s="15" t="n"/>
-      <c r="CQ76" s="12" t="n"/>
-      <c r="CR76" s="15" t="n"/>
-      <c r="CS76" s="14" t="n"/>
-      <c r="CT76" s="13" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+      <c r="BR76" s="64" t="n"/>
+      <c r="BS76" s="64" t="n"/>
+      <c r="BT76" s="64" t="n"/>
+      <c r="BU76" s="65" t="n"/>
+      <c r="BV76" s="64" t="n"/>
+      <c r="BW76" s="64" t="n"/>
+      <c r="BX76" s="64" t="n"/>
+      <c r="BY76" s="65" t="n"/>
+      <c r="BZ76" s="64" t="n"/>
+      <c r="CA76" s="64" t="n"/>
+      <c r="CB76" s="64" t="n"/>
+      <c r="CC76" s="65" t="n"/>
+      <c r="CD76" s="64" t="n"/>
+      <c r="CE76" s="64" t="n"/>
+      <c r="CF76" s="64" t="n"/>
+      <c r="CG76" s="64" t="n"/>
+      <c r="CH76" s="65" t="n"/>
+      <c r="CI76" s="64" t="n"/>
+      <c r="CJ76" s="64" t="n"/>
+      <c r="CK76" s="64" t="n"/>
+      <c r="CL76" s="65" t="n"/>
+      <c r="CM76" s="64" t="n"/>
+      <c r="CN76" s="64" t="n"/>
+      <c r="CO76" s="64" t="n"/>
+      <c r="CP76" s="64" t="n"/>
+      <c r="CQ76" s="65" t="n"/>
+      <c r="CR76" s="64" t="n"/>
+      <c r="CS76" s="64" t="n"/>
+      <c r="CT76" s="64" t="n"/>
       <c r="CU76" s="12" t="n"/>
       <c r="CV76" s="15" t="n"/>
       <c r="CW76" s="14" t="n"/>
       <c r="CX76" s="15" t="n"/>
     </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="70" t="inlineStr">
+    <row r="77" ht="13" customHeight="1">
+      <c r="A77" s="66" t="inlineStr">
+        <is>
+          <t>INT-05</t>
+        </is>
+      </c>
+      <c r="B77" s="67" t="inlineStr">
+        <is>
+          <t>★ RFSU — Ready For Start Up Planta Total</t>
+        </is>
+      </c>
+      <c r="C77" s="62" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="D77" s="66" t="inlineStr">
+        <is>
+          <t>31/01/2028</t>
+        </is>
+      </c>
+      <c r="E77" s="69" t="inlineStr">
+        <is>
+          <t>31/01/2028</t>
+        </is>
+      </c>
+      <c r="F77" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="12" t="n"/>
+      <c r="H77" s="15" t="n"/>
+      <c r="I77" s="14" t="n"/>
+      <c r="J77" s="15" t="n"/>
+      <c r="K77" s="14" t="n"/>
+      <c r="L77" s="16" t="n"/>
+      <c r="M77" s="14" t="n"/>
+      <c r="N77" s="15" t="n"/>
+      <c r="O77" s="14" t="n"/>
+      <c r="P77" s="16" t="n"/>
+      <c r="Q77" s="14" t="n"/>
+      <c r="R77" s="15" t="n"/>
+      <c r="S77" s="14" t="n"/>
+      <c r="T77" s="15" t="n"/>
+      <c r="U77" s="12" t="n"/>
+      <c r="V77" s="15" t="n"/>
+      <c r="W77" s="14" t="n"/>
+      <c r="X77" s="15" t="n"/>
+      <c r="Y77" s="12" t="n"/>
+      <c r="Z77" s="15" t="n"/>
+      <c r="AA77" s="14" t="n"/>
+      <c r="AB77" s="15" t="n"/>
+      <c r="AC77" s="12" t="n"/>
+      <c r="AD77" s="15" t="n"/>
+      <c r="AE77" s="14" t="n"/>
+      <c r="AF77" s="15" t="n"/>
+      <c r="AG77" s="14" t="n"/>
+      <c r="AH77" s="16" t="n"/>
+      <c r="AI77" s="14" t="n"/>
+      <c r="AJ77" s="15" t="n"/>
+      <c r="AK77" s="14" t="n"/>
+      <c r="AL77" s="16" t="n"/>
+      <c r="AM77" s="14" t="n"/>
+      <c r="AN77" s="15" t="n"/>
+      <c r="AO77" s="14" t="n"/>
+      <c r="AP77" s="16" t="n"/>
+      <c r="AQ77" s="14" t="n"/>
+      <c r="AR77" s="15" t="n"/>
+      <c r="AS77" s="14" t="n"/>
+      <c r="AT77" s="15" t="n"/>
+      <c r="AU77" s="12" t="n"/>
+      <c r="AV77" s="15" t="n"/>
+      <c r="AW77" s="14" t="n"/>
+      <c r="AX77" s="15" t="n"/>
+      <c r="AY77" s="12" t="n"/>
+      <c r="AZ77" s="15" t="n"/>
+      <c r="BA77" s="14" t="n"/>
+      <c r="BB77" s="15" t="n"/>
+      <c r="BC77" s="12" t="n"/>
+      <c r="BD77" s="15" t="n"/>
+      <c r="BE77" s="14" t="n"/>
+      <c r="BF77" s="15" t="n"/>
+      <c r="BG77" s="14" t="n"/>
+      <c r="BH77" s="16" t="n"/>
+      <c r="BI77" s="14" t="n"/>
+      <c r="BJ77" s="15" t="n"/>
+      <c r="BK77" s="14" t="n"/>
+      <c r="BL77" s="16" t="n"/>
+      <c r="BM77" s="14" t="n"/>
+      <c r="BN77" s="15" t="n"/>
+      <c r="BO77" s="14" t="n"/>
+      <c r="BP77" s="16" t="n"/>
+      <c r="BQ77" s="14" t="n"/>
+      <c r="BR77" s="15" t="n"/>
+      <c r="BS77" s="14" t="n"/>
+      <c r="BT77" s="15" t="n"/>
+      <c r="BU77" s="12" t="n"/>
+      <c r="BV77" s="15" t="n"/>
+      <c r="BW77" s="14" t="n"/>
+      <c r="BX77" s="15" t="n"/>
+      <c r="BY77" s="12" t="n"/>
+      <c r="BZ77" s="15" t="n"/>
+      <c r="CA77" s="14" t="n"/>
+      <c r="CB77" s="15" t="n"/>
+      <c r="CC77" s="12" t="n"/>
+      <c r="CD77" s="15" t="n"/>
+      <c r="CE77" s="14" t="n"/>
+      <c r="CF77" s="15" t="n"/>
+      <c r="CG77" s="14" t="n"/>
+      <c r="CH77" s="16" t="n"/>
+      <c r="CI77" s="14" t="n"/>
+      <c r="CJ77" s="15" t="n"/>
+      <c r="CK77" s="14" t="n"/>
+      <c r="CL77" s="16" t="n"/>
+      <c r="CM77" s="14" t="n"/>
+      <c r="CN77" s="15" t="n"/>
+      <c r="CO77" s="14" t="n"/>
+      <c r="CP77" s="15" t="n"/>
+      <c r="CQ77" s="12" t="n"/>
+      <c r="CR77" s="15" t="n"/>
+      <c r="CS77" s="14" t="n"/>
+      <c r="CT77" s="13" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="CU77" s="12" t="n"/>
+      <c r="CV77" s="15" t="n"/>
+      <c r="CW77" s="14" t="n"/>
+      <c r="CX77" s="15" t="n"/>
+    </row>
+    <row r="78" ht="14" customHeight="1">
+      <c r="A78" s="60" t="inlineStr">
+        <is>
+          <t>INT-06</t>
+        </is>
+      </c>
+      <c r="B78" s="61" t="inlineStr">
+        <is>
+          <t>SAT PMS — Pruebas en Sitio (100% puntos E/S)</t>
+        </is>
+      </c>
+      <c r="C78" s="62" t="inlineStr">
+        <is>
+          <t>PMS</t>
+        </is>
+      </c>
+      <c r="D78" s="62" t="inlineStr">
+        <is>
+          <t>01/10/2027</t>
+        </is>
+      </c>
+      <c r="E78" s="62" t="inlineStr">
+        <is>
+          <t>15/12/2027</t>
+        </is>
+      </c>
+      <c r="F78" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="12" t="n"/>
+      <c r="H78" s="15" t="n"/>
+      <c r="I78" s="14" t="n"/>
+      <c r="J78" s="15" t="n"/>
+      <c r="K78" s="14" t="n"/>
+      <c r="L78" s="16" t="n"/>
+      <c r="M78" s="14" t="n"/>
+      <c r="N78" s="15" t="n"/>
+      <c r="O78" s="14" t="n"/>
+      <c r="P78" s="16" t="n"/>
+      <c r="Q78" s="14" t="n"/>
+      <c r="R78" s="15" t="n"/>
+      <c r="S78" s="14" t="n"/>
+      <c r="T78" s="15" t="n"/>
+      <c r="U78" s="12" t="n"/>
+      <c r="V78" s="15" t="n"/>
+      <c r="W78" s="14" t="n"/>
+      <c r="X78" s="15" t="n"/>
+      <c r="Y78" s="12" t="n"/>
+      <c r="Z78" s="15" t="n"/>
+      <c r="AA78" s="14" t="n"/>
+      <c r="AB78" s="15" t="n"/>
+      <c r="AC78" s="12" t="n"/>
+      <c r="AD78" s="15" t="n"/>
+      <c r="AE78" s="14" t="n"/>
+      <c r="AF78" s="15" t="n"/>
+      <c r="AG78" s="14" t="n"/>
+      <c r="AH78" s="16" t="n"/>
+      <c r="AI78" s="14" t="n"/>
+      <c r="AJ78" s="15" t="n"/>
+      <c r="AK78" s="14" t="n"/>
+      <c r="AL78" s="16" t="n"/>
+      <c r="AM78" s="14" t="n"/>
+      <c r="AN78" s="15" t="n"/>
+      <c r="AO78" s="14" t="n"/>
+      <c r="AP78" s="16" t="n"/>
+      <c r="AQ78" s="14" t="n"/>
+      <c r="AR78" s="15" t="n"/>
+      <c r="AS78" s="14" t="n"/>
+      <c r="AT78" s="15" t="n"/>
+      <c r="AU78" s="12" t="n"/>
+      <c r="AV78" s="15" t="n"/>
+      <c r="AW78" s="14" t="n"/>
+      <c r="AX78" s="15" t="n"/>
+      <c r="AY78" s="12" t="n"/>
+      <c r="AZ78" s="15" t="n"/>
+      <c r="BA78" s="14" t="n"/>
+      <c r="BB78" s="15" t="n"/>
+      <c r="BC78" s="12" t="n"/>
+      <c r="BD78" s="15" t="n"/>
+      <c r="BE78" s="14" t="n"/>
+      <c r="BF78" s="15" t="n"/>
+      <c r="BG78" s="14" t="n"/>
+      <c r="BH78" s="16" t="n"/>
+      <c r="BI78" s="14" t="n"/>
+      <c r="BJ78" s="15" t="n"/>
+      <c r="BK78" s="14" t="n"/>
+      <c r="BL78" s="16" t="n"/>
+      <c r="BM78" s="14" t="n"/>
+      <c r="BN78" s="15" t="n"/>
+      <c r="BO78" s="14" t="n"/>
+      <c r="BP78" s="16" t="n"/>
+      <c r="BQ78" s="14" t="n"/>
+      <c r="BR78" s="15" t="n"/>
+      <c r="BS78" s="14" t="n"/>
+      <c r="BT78" s="15" t="n"/>
+      <c r="BU78" s="12" t="n"/>
+      <c r="BV78" s="15" t="n"/>
+      <c r="BW78" s="14" t="n"/>
+      <c r="BX78" s="15" t="n"/>
+      <c r="BY78" s="12" t="n"/>
+      <c r="BZ78" s="15" t="n"/>
+      <c r="CA78" s="14" t="n"/>
+      <c r="CB78" s="15" t="n"/>
+      <c r="CC78" s="24" t="n"/>
+      <c r="CD78" s="23" t="n"/>
+      <c r="CE78" s="23" t="n"/>
+      <c r="CF78" s="23" t="n"/>
+      <c r="CG78" s="23" t="n"/>
+      <c r="CH78" s="24" t="n"/>
+      <c r="CI78" s="23" t="n"/>
+      <c r="CJ78" s="23" t="n"/>
+      <c r="CK78" s="23" t="n"/>
+      <c r="CL78" s="24" t="n"/>
+      <c r="CM78" s="23" t="n"/>
+      <c r="CN78" s="15" t="n"/>
+      <c r="CO78" s="14" t="n"/>
+      <c r="CP78" s="15" t="n"/>
+      <c r="CQ78" s="12" t="n"/>
+      <c r="CR78" s="15" t="n"/>
+      <c r="CS78" s="14" t="n"/>
+      <c r="CT78" s="15" t="n"/>
+      <c r="CU78" s="12" t="n"/>
+      <c r="CV78" s="15" t="n"/>
+      <c r="CW78" s="14" t="n"/>
+      <c r="CX78" s="15" t="n"/>
+    </row>
+    <row r="79" ht="14" customHeight="1">
+      <c r="A79" s="60" t="inlineStr">
+        <is>
+          <t>INT-07</t>
+        </is>
+      </c>
+      <c r="B79" s="61" t="inlineStr">
+        <is>
+          <t>Capacitación PMS — 1ra Instancia (Ingeniería y Mantenimiento)</t>
+        </is>
+      </c>
+      <c r="C79" s="62" t="inlineStr">
+        <is>
+          <t>PMS</t>
+        </is>
+      </c>
+      <c r="D79" s="62" t="inlineStr">
+        <is>
+          <t>05/02/2028</t>
+        </is>
+      </c>
+      <c r="E79" s="62" t="inlineStr">
+        <is>
+          <t>09/02/2028</t>
+        </is>
+      </c>
+      <c r="F79" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="12" t="n"/>
+      <c r="H79" s="15" t="n"/>
+      <c r="I79" s="14" t="n"/>
+      <c r="J79" s="15" t="n"/>
+      <c r="K79" s="14" t="n"/>
+      <c r="L79" s="16" t="n"/>
+      <c r="M79" s="14" t="n"/>
+      <c r="N79" s="15" t="n"/>
+      <c r="O79" s="14" t="n"/>
+      <c r="P79" s="16" t="n"/>
+      <c r="Q79" s="14" t="n"/>
+      <c r="R79" s="15" t="n"/>
+      <c r="S79" s="14" t="n"/>
+      <c r="T79" s="15" t="n"/>
+      <c r="U79" s="12" t="n"/>
+      <c r="V79" s="15" t="n"/>
+      <c r="W79" s="14" t="n"/>
+      <c r="X79" s="15" t="n"/>
+      <c r="Y79" s="12" t="n"/>
+      <c r="Z79" s="15" t="n"/>
+      <c r="AA79" s="14" t="n"/>
+      <c r="AB79" s="15" t="n"/>
+      <c r="AC79" s="12" t="n"/>
+      <c r="AD79" s="15" t="n"/>
+      <c r="AE79" s="14" t="n"/>
+      <c r="AF79" s="15" t="n"/>
+      <c r="AG79" s="14" t="n"/>
+      <c r="AH79" s="16" t="n"/>
+      <c r="AI79" s="14" t="n"/>
+      <c r="AJ79" s="15" t="n"/>
+      <c r="AK79" s="14" t="n"/>
+      <c r="AL79" s="16" t="n"/>
+      <c r="AM79" s="14" t="n"/>
+      <c r="AN79" s="15" t="n"/>
+      <c r="AO79" s="14" t="n"/>
+      <c r="AP79" s="16" t="n"/>
+      <c r="AQ79" s="14" t="n"/>
+      <c r="AR79" s="15" t="n"/>
+      <c r="AS79" s="14" t="n"/>
+      <c r="AT79" s="15" t="n"/>
+      <c r="AU79" s="12" t="n"/>
+      <c r="AV79" s="15" t="n"/>
+      <c r="AW79" s="14" t="n"/>
+      <c r="AX79" s="15" t="n"/>
+      <c r="AY79" s="12" t="n"/>
+      <c r="AZ79" s="15" t="n"/>
+      <c r="BA79" s="14" t="n"/>
+      <c r="BB79" s="15" t="n"/>
+      <c r="BC79" s="12" t="n"/>
+      <c r="BD79" s="15" t="n"/>
+      <c r="BE79" s="14" t="n"/>
+      <c r="BF79" s="15" t="n"/>
+      <c r="BG79" s="14" t="n"/>
+      <c r="BH79" s="16" t="n"/>
+      <c r="BI79" s="14" t="n"/>
+      <c r="BJ79" s="15" t="n"/>
+      <c r="BK79" s="14" t="n"/>
+      <c r="BL79" s="16" t="n"/>
+      <c r="BM79" s="14" t="n"/>
+      <c r="BN79" s="15" t="n"/>
+      <c r="BO79" s="14" t="n"/>
+      <c r="BP79" s="16" t="n"/>
+      <c r="BQ79" s="14" t="n"/>
+      <c r="BR79" s="15" t="n"/>
+      <c r="BS79" s="14" t="n"/>
+      <c r="BT79" s="15" t="n"/>
+      <c r="BU79" s="12" t="n"/>
+      <c r="BV79" s="15" t="n"/>
+      <c r="BW79" s="14" t="n"/>
+      <c r="BX79" s="15" t="n"/>
+      <c r="BY79" s="12" t="n"/>
+      <c r="BZ79" s="15" t="n"/>
+      <c r="CA79" s="14" t="n"/>
+      <c r="CB79" s="15" t="n"/>
+      <c r="CC79" s="12" t="n"/>
+      <c r="CD79" s="15" t="n"/>
+      <c r="CE79" s="14" t="n"/>
+      <c r="CF79" s="15" t="n"/>
+      <c r="CG79" s="14" t="n"/>
+      <c r="CH79" s="16" t="n"/>
+      <c r="CI79" s="14" t="n"/>
+      <c r="CJ79" s="15" t="n"/>
+      <c r="CK79" s="14" t="n"/>
+      <c r="CL79" s="16" t="n"/>
+      <c r="CM79" s="14" t="n"/>
+      <c r="CN79" s="15" t="n"/>
+      <c r="CO79" s="14" t="n"/>
+      <c r="CP79" s="15" t="n"/>
+      <c r="CQ79" s="12" t="n"/>
+      <c r="CR79" s="15" t="n"/>
+      <c r="CS79" s="14" t="n"/>
+      <c r="CT79" s="15" t="n"/>
+      <c r="CU79" s="24" t="n"/>
+      <c r="CV79" s="15" t="n"/>
+      <c r="CW79" s="14" t="n"/>
+      <c r="CX79" s="15" t="n"/>
+    </row>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="60" t="inlineStr">
+        <is>
+          <t>INT-08</t>
+        </is>
+      </c>
+      <c r="B80" s="61" t="inlineStr">
+        <is>
+          <t>Capacitación PMS — 2da Instancia (Operación)</t>
+        </is>
+      </c>
+      <c r="C80" s="62" t="inlineStr">
+        <is>
+          <t>PMS</t>
+        </is>
+      </c>
+      <c r="D80" s="62" t="inlineStr">
+        <is>
+          <t>03/03/2028</t>
+        </is>
+      </c>
+      <c r="E80" s="62" t="inlineStr">
+        <is>
+          <t>07/03/2028</t>
+        </is>
+      </c>
+      <c r="F80" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="12" t="n"/>
+      <c r="H80" s="15" t="n"/>
+      <c r="I80" s="14" t="n"/>
+      <c r="J80" s="15" t="n"/>
+      <c r="K80" s="14" t="n"/>
+      <c r="L80" s="16" t="n"/>
+      <c r="M80" s="14" t="n"/>
+      <c r="N80" s="15" t="n"/>
+      <c r="O80" s="14" t="n"/>
+      <c r="P80" s="16" t="n"/>
+      <c r="Q80" s="14" t="n"/>
+      <c r="R80" s="15" t="n"/>
+      <c r="S80" s="14" t="n"/>
+      <c r="T80" s="15" t="n"/>
+      <c r="U80" s="12" t="n"/>
+      <c r="V80" s="15" t="n"/>
+      <c r="W80" s="14" t="n"/>
+      <c r="X80" s="15" t="n"/>
+      <c r="Y80" s="12" t="n"/>
+      <c r="Z80" s="15" t="n"/>
+      <c r="AA80" s="14" t="n"/>
+      <c r="AB80" s="15" t="n"/>
+      <c r="AC80" s="12" t="n"/>
+      <c r="AD80" s="15" t="n"/>
+      <c r="AE80" s="14" t="n"/>
+      <c r="AF80" s="15" t="n"/>
+      <c r="AG80" s="14" t="n"/>
+      <c r="AH80" s="16" t="n"/>
+      <c r="AI80" s="14" t="n"/>
+      <c r="AJ80" s="15" t="n"/>
+      <c r="AK80" s="14" t="n"/>
+      <c r="AL80" s="16" t="n"/>
+      <c r="AM80" s="14" t="n"/>
+      <c r="AN80" s="15" t="n"/>
+      <c r="AO80" s="14" t="n"/>
+      <c r="AP80" s="16" t="n"/>
+      <c r="AQ80" s="14" t="n"/>
+      <c r="AR80" s="15" t="n"/>
+      <c r="AS80" s="14" t="n"/>
+      <c r="AT80" s="15" t="n"/>
+      <c r="AU80" s="12" t="n"/>
+      <c r="AV80" s="15" t="n"/>
+      <c r="AW80" s="14" t="n"/>
+      <c r="AX80" s="15" t="n"/>
+      <c r="AY80" s="12" t="n"/>
+      <c r="AZ80" s="15" t="n"/>
+      <c r="BA80" s="14" t="n"/>
+      <c r="BB80" s="15" t="n"/>
+      <c r="BC80" s="12" t="n"/>
+      <c r="BD80" s="15" t="n"/>
+      <c r="BE80" s="14" t="n"/>
+      <c r="BF80" s="15" t="n"/>
+      <c r="BG80" s="14" t="n"/>
+      <c r="BH80" s="16" t="n"/>
+      <c r="BI80" s="14" t="n"/>
+      <c r="BJ80" s="15" t="n"/>
+      <c r="BK80" s="14" t="n"/>
+      <c r="BL80" s="16" t="n"/>
+      <c r="BM80" s="14" t="n"/>
+      <c r="BN80" s="15" t="n"/>
+      <c r="BO80" s="14" t="n"/>
+      <c r="BP80" s="16" t="n"/>
+      <c r="BQ80" s="14" t="n"/>
+      <c r="BR80" s="15" t="n"/>
+      <c r="BS80" s="14" t="n"/>
+      <c r="BT80" s="15" t="n"/>
+      <c r="BU80" s="12" t="n"/>
+      <c r="BV80" s="15" t="n"/>
+      <c r="BW80" s="14" t="n"/>
+      <c r="BX80" s="15" t="n"/>
+      <c r="BY80" s="12" t="n"/>
+      <c r="BZ80" s="15" t="n"/>
+      <c r="CA80" s="14" t="n"/>
+      <c r="CB80" s="15" t="n"/>
+      <c r="CC80" s="12" t="n"/>
+      <c r="CD80" s="15" t="n"/>
+      <c r="CE80" s="14" t="n"/>
+      <c r="CF80" s="15" t="n"/>
+      <c r="CG80" s="14" t="n"/>
+      <c r="CH80" s="16" t="n"/>
+      <c r="CI80" s="14" t="n"/>
+      <c r="CJ80" s="15" t="n"/>
+      <c r="CK80" s="14" t="n"/>
+      <c r="CL80" s="16" t="n"/>
+      <c r="CM80" s="14" t="n"/>
+      <c r="CN80" s="15" t="n"/>
+      <c r="CO80" s="14" t="n"/>
+      <c r="CP80" s="15" t="n"/>
+      <c r="CQ80" s="12" t="n"/>
+      <c r="CR80" s="15" t="n"/>
+      <c r="CS80" s="14" t="n"/>
+      <c r="CT80" s="15" t="n"/>
+      <c r="CU80" s="12" t="n"/>
+      <c r="CV80" s="15" t="n"/>
+      <c r="CW80" s="14" t="n"/>
+      <c r="CX80" s="15" t="n"/>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="70" t="inlineStr">
         <is>
           <t>★ CADENA CRÍTICA S#3: 37 CCMs BT → FP-IC 31/AGO/2026 → FAT 19/ABR/2027 → Despacho 14/MAY/2027  |  Holguras: FAT S3 +35d | Despacho S3 +45d | iFAT +3d | RFSU 31/ENE/2028 = IGUAL EN P6 ✅</t>
         </is>
@@ -10032,35 +10544,35 @@
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="A81:CX81"/>
     <mergeCell ref="AP4:AT4"/>
+    <mergeCell ref="A72:CX72"/>
     <mergeCell ref="P4:T4"/>
     <mergeCell ref="A13:CX13"/>
     <mergeCell ref="AL4:AO4"/>
-    <mergeCell ref="A44:CX44"/>
     <mergeCell ref="BU4:BX4"/>
-    <mergeCell ref="A77:CX77"/>
-    <mergeCell ref="A64:CX64"/>
     <mergeCell ref="BP4:BT4"/>
     <mergeCell ref="U4:X4"/>
     <mergeCell ref="AP3:CP3"/>
     <mergeCell ref="A1:CX1"/>
+    <mergeCell ref="A45:CX45"/>
     <mergeCell ref="Y4:AB4"/>
     <mergeCell ref="CQ3:CX3"/>
     <mergeCell ref="BH4:BK4"/>
     <mergeCell ref="BY4:CB4"/>
     <mergeCell ref="A6:CX6"/>
     <mergeCell ref="CU4:CX4"/>
+    <mergeCell ref="A65:CX65"/>
     <mergeCell ref="AC4:AG4"/>
     <mergeCell ref="CC4:CG4"/>
-    <mergeCell ref="A25:CX25"/>
     <mergeCell ref="AU4:AX4"/>
     <mergeCell ref="AH4:AK4"/>
     <mergeCell ref="AY4:BB4"/>
     <mergeCell ref="G3:AO3"/>
     <mergeCell ref="CH4:CK4"/>
     <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A26:CX26"/>
     <mergeCell ref="A2:CX2"/>
-    <mergeCell ref="A71:CX71"/>
     <mergeCell ref="BC4:BG4"/>
     <mergeCell ref="CL4:CP4"/>
     <mergeCell ref="L4:O4"/>
@@ -10217,12 +10729,12 @@
       </c>
       <c r="I6" s="81" t="inlineStr">
         <is>
-          <t>Demora en procura y fabricación tablero PMS. PMS tiene holgura amplia (222d vs P6)</t>
+          <t>Arquitectura 800XA + lista señales (30% reserva) + protocolo Modbus TCP/IP no se pueden cerrar → FAT Maqueta Sep-Oct en riesgo. PMS tiene holgura amplia (222d vs P6) pero FP-P1 tardío comprime FAT Tableros</t>
         </is>
       </c>
       <c r="J6" s="82" t="inlineStr">
         <is>
-          <t>CONGELAR DISEÑO IB. Cambios posteriores → Nota de Cambio + impacto costo/plazo</t>
+          <t>CONGELAR: arquitectura 800XA + lista señales (30% reserva mín.) + protocolo Modbus TCP/IP (acordado Oct-2025, reunión AESA-INAUCO-ABB). Cambios → NC + impacto costo/plazo</t>
         </is>
       </c>
     </row>
@@ -11177,7 +11689,7 @@
       </c>
       <c r="I18" s="115" t="inlineStr">
         <is>
-          <t>AESA no confirma CCM7 → ABB no puede cerrar diseño ID → toda la cadena se retrasa</t>
+          <t>AESA no confirma CCM7 → ABB no puede cerrar ID S3. VFDs DP-VFD-24210 A/B/C (SE#3) y DP-VFD-23310 A/B/C (SE#4) en scope PMS vía PROFINET — la decisión afecta señales del sistema</t>
         </is>
       </c>
     </row>
@@ -12022,7 +12534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:J41"/>
+  <dimension ref="B1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12452,7 +12964,7 @@
       </c>
       <c r="J12" s="88" t="inlineStr">
         <is>
-          <t>CONGELAR DISEÑO IB. Cambios posteriores → Nota de Cambio + impacto costo/plazo</t>
+          <t>CONGELAR: arquitectura 800XA + lista señales (30% reserva mín.) + protocolo Modbus TCP/IP (acordado Oct-2025, reunión AESA-INAUCO-ABB). Cambios → NC + impacto costo/plazo</t>
         </is>
       </c>
     </row>
@@ -12511,7 +13023,7 @@
       </c>
       <c r="C14" s="77" t="inlineStr">
         <is>
-          <t>FAT Maqueta PMS — pruebas funcionales previas</t>
+          <t>FAT Maqueta PMS — Pruebas Tempranas (ET sec.20)</t>
         </is>
       </c>
       <c r="D14" s="142" t="inlineStr">
@@ -12546,7 +13058,7 @@
       </c>
       <c r="J14" s="82" t="inlineStr">
         <is>
-          <t>Sep-Oct 2026. Fábrica ABB Buenos Aires. Asiste AESA según acuerdo KOM</t>
+          <t>Sep-Oct 2026. Fábrica ABB Buenos Aires. Pruebas sobre mock-up PMS+CCM+AC800M red.+PROFINET. AESA + Contratista SCADA participan OBLIGATORIAMENTE (ET ACAL-00102-ET-E-0005 sec.20). ⚠ Planificar viaje BsAs</t>
         </is>
       </c>
     </row>
@@ -12692,24 +13204,24 @@
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="139" t="inlineStr">
-        <is>
-          <t>FP-S4-1</t>
-        </is>
-      </c>
-      <c r="C18" s="140" t="inlineStr">
-        <is>
-          <t>◆ FREEZING POINT — Ing. Básica Sala #4</t>
-        </is>
-      </c>
-      <c r="D18" s="136" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="E18" s="138" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
+      <c r="B18" s="141" t="inlineStr">
+        <is>
+          <t>P-10</t>
+        </is>
+      </c>
+      <c r="C18" s="77" t="inlineStr">
+        <is>
+          <t>▶ DESPACHO Tablero PMS — 14-MAY-2027</t>
+        </is>
+      </c>
+      <c r="D18" s="142" t="inlineStr">
+        <is>
+          <t>PMS</t>
+        </is>
+      </c>
+      <c r="E18" s="143" t="inlineStr">
+        <is>
+          <t>14/05/2027</t>
         </is>
       </c>
       <c r="F18" s="136" t="inlineStr">
@@ -12732,21 +13244,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J18" s="88" t="inlineStr">
-        <is>
-          <t>CONGELAR. Inicio procura celdas MT (Turquía — lead time ~6 meses). CRÍTICO para timing logístico</t>
+      <c r="J18" s="82" t="inlineStr">
+        <is>
+          <t>OC deadline: 14-MAY-2027 (alineado S#3). Gabinetes 102-PMS-001 y 102-PMS-101 despa chados desde BsAs hacia Vaca Muerta</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="B19" s="139" t="inlineStr">
         <is>
-          <t>FP-S4-2</t>
+          <t>FP-S4-1</t>
         </is>
       </c>
       <c r="C19" s="140" t="inlineStr">
         <is>
-          <t>◆ FREEZING POINT — Ing. Detalle Sala #4</t>
+          <t>◆ FREEZING POINT — Ing. Básica Sala #4</t>
         </is>
       </c>
       <c r="D19" s="136" t="inlineStr">
@@ -12756,7 +13268,7 @@
       </c>
       <c r="E19" s="138" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="F19" s="136" t="inlineStr">
@@ -12781,113 +13293,113 @@
       </c>
       <c r="J19" s="88" t="inlineStr">
         <is>
-          <t>CONGELAR diseño detalle. Inicio fabricación tableros auxiliares BsAs</t>
+          <t>CONGELAR. Inicio procura celdas MT (Turquía — lead time ~6 meses). CRÍTICO para timing logístico</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="B20" s="139" t="inlineStr">
         <is>
+          <t>FP-S4-2</t>
+        </is>
+      </c>
+      <c r="C20" s="140" t="inlineStr">
+        <is>
+          <t>◆ FREEZING POINT — Ing. Detalle Sala #4</t>
+        </is>
+      </c>
+      <c r="D20" s="136" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="E20" s="138" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="136" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="137" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H20" s="138" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I20" s="136" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="88" t="inlineStr">
+        <is>
+          <t>CONGELAR diseño detalle. Inicio fabricación tableros auxiliares BsAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="139" t="inlineStr">
+        <is>
           <t>FP-S4-3</t>
         </is>
       </c>
-      <c r="C20" s="140" t="inlineStr">
+      <c r="C21" s="140" t="inlineStr">
         <is>
           <t>◆ FREEZING POINT — Ing. Constructiva Sala #4  ← CIERRA INGENIERÍA S4</t>
         </is>
       </c>
-      <c r="D20" s="136" t="inlineStr">
+      <c r="D21" s="136" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="E20" s="138" t="inlineStr">
+      <c r="E21" s="138" t="inlineStr">
         <is>
           <t>28/08/2026</t>
         </is>
       </c>
-      <c r="F20" s="136" t="inlineStr">
+      <c r="F21" s="136" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="137" t="inlineStr">
+      <c r="G21" s="137" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="H20" s="138" t="inlineStr">
+      <c r="H21" s="138" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I20" s="136" t="inlineStr">
+      <c r="I21" s="136" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J20" s="88" t="inlineStr">
+      <c r="J21" s="88" t="inlineStr">
         <is>
           <t>ÚLTIMO FP DE S4 (24-AGO). Cierre total ingeniería Sala #4. Sin hito equivalente en P6 ⚠</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="144" t="inlineStr">
-        <is>
-          <t>S4-10</t>
-        </is>
-      </c>
-      <c r="C21" s="145" t="inlineStr">
-        <is>
-          <t>Ensayos Celdas y Tableros MT Sala #4</t>
-        </is>
-      </c>
-      <c r="D21" s="146" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="E21" s="147" t="inlineStr">
-        <is>
-          <t>23/11/2026</t>
-        </is>
-      </c>
-      <c r="F21" s="136" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" s="137" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H21" s="138" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I21" s="136" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J21" s="148" t="inlineStr">
-        <is>
-          <t>20 días. Pruebas en Brasil — ABB + AESA inspeccionan</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="B22" s="144" t="inlineStr">
         <is>
-          <t>S4-13</t>
+          <t>S4-10</t>
         </is>
       </c>
       <c r="C22" s="145" t="inlineStr">
         <is>
-          <t>FAT Sala Eléctrica #4 (Shelter completo)</t>
+          <t>Ensayos Celdas y Tableros MT Sala #4</t>
         </is>
       </c>
       <c r="D22" s="146" t="inlineStr">
@@ -12897,7 +13409,7 @@
       </c>
       <c r="E22" s="147" t="inlineStr">
         <is>
-          <t>16/03/2027</t>
+          <t>23/11/2026</t>
         </is>
       </c>
       <c r="F22" s="136" t="inlineStr">
@@ -12922,19 +13434,19 @@
       </c>
       <c r="J22" s="148" t="inlineStr">
         <is>
-          <t>8 días. FAT integrado del Shelter completo. Asiste AESA + Cliente</t>
+          <t>20 días. Pruebas en Brasil — ABB + AESA inspeccionan</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="B23" s="144" t="inlineStr">
         <is>
-          <t>S4-14</t>
+          <t>S4-13</t>
         </is>
       </c>
       <c r="C23" s="145" t="inlineStr">
         <is>
-          <t>▶ DESPACHO Sala #4 → Vaca Muerta</t>
+          <t>FAT Sala Eléctrica #4 (Shelter completo)</t>
         </is>
       </c>
       <c r="D23" s="146" t="inlineStr">
@@ -12944,7 +13456,7 @@
       </c>
       <c r="E23" s="147" t="inlineStr">
         <is>
-          <t>08/04/2027</t>
+          <t>16/03/2027</t>
         </is>
       </c>
       <c r="F23" s="136" t="inlineStr">
@@ -12969,113 +13481,113 @@
       </c>
       <c r="J23" s="148" t="inlineStr">
         <is>
-          <t>OC deadline: 08-ABR-2027. P6 inicio montaje campo: 28-JUN-2027. Holgura: 81 días</t>
+          <t>8 días. FAT integrado del Shelter completo. Asiste AESA + Cliente</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="B24" s="144" t="inlineStr">
         <is>
+          <t>S4-14</t>
+        </is>
+      </c>
+      <c r="C24" s="145" t="inlineStr">
+        <is>
+          <t>▶ DESPACHO Sala #4 → Vaca Muerta</t>
+        </is>
+      </c>
+      <c r="D24" s="146" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="E24" s="147" t="inlineStr">
+        <is>
+          <t>08/04/2027</t>
+        </is>
+      </c>
+      <c r="F24" s="136" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="137" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H24" s="138" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I24" s="136" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="148" t="inlineStr">
+        <is>
+          <t>OC deadline: 08-ABR-2027. P6 inicio montaje campo: 28-JUN-2027. Holgura: 81 días</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="144" t="inlineStr">
+        <is>
           <t>S4-15</t>
         </is>
       </c>
-      <c r="C24" s="145" t="inlineStr">
+      <c r="C25" s="145" t="inlineStr">
         <is>
           <t>★ ENTREGA S#4 — Cumplimiento OC 4508944973</t>
         </is>
       </c>
-      <c r="D24" s="146" t="inlineStr">
+      <c r="D25" s="146" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="E24" s="147" t="inlineStr">
+      <c r="E25" s="147" t="inlineStr">
         <is>
           <t>08/04/2027</t>
         </is>
       </c>
-      <c r="F24" s="136" t="inlineStr">
+      <c r="F25" s="136" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G24" s="137" t="inlineStr">
+      <c r="G25" s="137" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="H24" s="138" t="inlineStr">
+      <c r="H25" s="138" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I24" s="136" t="inlineStr">
+      <c r="I25" s="136" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J24" s="148" t="inlineStr">
+      <c r="J25" s="148" t="inlineStr">
         <is>
           <t>FECHA CONTRACTUAL: 08-ABR-2027 (11 meses). Penalidad si excede: 1%/semana, tope 10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="102" t="inlineStr">
-        <is>
-          <t>FP-S3-1</t>
-        </is>
-      </c>
-      <c r="C25" s="132" t="inlineStr">
-        <is>
-          <t>◆ FREEZING POINT — Ing. Básica Sala #3</t>
-        </is>
-      </c>
-      <c r="D25" s="104" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="E25" s="102" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="F25" s="136" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="137" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H25" s="138" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I25" s="136" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J25" s="93" t="inlineStr">
-        <is>
-          <t>1 semana después que S4 (26-JUN). CONGELAR. Inicio procura ductos barras (Turquía)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="B26" s="102" t="inlineStr">
         <is>
-          <t>FP-S3-2</t>
+          <t>FP-S3-1</t>
         </is>
       </c>
       <c r="C26" s="132" t="inlineStr">
         <is>
-          <t>◆ FREEZING POINT — Ing. Detalle Sala #3</t>
+          <t>◆ FREEZING POINT — Ing. Básica Sala #3</t>
         </is>
       </c>
       <c r="D26" s="104" t="inlineStr">
@@ -13085,7 +13597,7 @@
       </c>
       <c r="E26" s="102" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="F26" s="136" t="inlineStr">
@@ -13110,19 +13622,19 @@
       </c>
       <c r="J26" s="93" t="inlineStr">
         <is>
-          <t>CONGELAR diseño detalle S3. Inicio fabricación tableros BT (Brasil). Sin hito P6 ⚠</t>
+          <t>1 semana después que S4 (26-JUN). CONGELAR. Inicio procura ductos barras (Turquía)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="102" t="inlineStr">
         <is>
-          <t>FP-S3-3</t>
+          <t>FP-S3-2</t>
         </is>
       </c>
       <c r="C27" s="132" t="inlineStr">
         <is>
-          <t>◆ FREEZING POINT — Ing. Constructiva Sala #3  ← ÚLTIMO FP ABB</t>
+          <t>◆ FREEZING POINT — Ing. Detalle Sala #3</t>
         </is>
       </c>
       <c r="D27" s="104" t="inlineStr">
@@ -13132,7 +13644,7 @@
       </c>
       <c r="E27" s="102" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="F27" s="136" t="inlineStr">
@@ -13157,19 +13669,19 @@
       </c>
       <c r="J27" s="93" t="inlineStr">
         <is>
-          <t>★ HITO CLAVE: ÚLTIMO FREEZING POINT DE TODO EL PROYECTO ABB — 31-AGO-2026. Cierra toda la ingeniería. Sin hito en P6 ⚠</t>
+          <t>CONGELAR diseño detalle S3. Inicio fabricación tableros BT (Brasil). Sin hito P6 ⚠</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="B28" s="102" t="inlineStr">
         <is>
-          <t>S3-10</t>
+          <t>FP-S3-3</t>
         </is>
       </c>
       <c r="C28" s="132" t="inlineStr">
         <is>
-          <t>Ensayos Celdas y Tableros BT Sala #3</t>
+          <t>◆ FREEZING POINT — Ing. Constructiva Sala #3  ← ÚLTIMO FP ABB</t>
         </is>
       </c>
       <c r="D28" s="104" t="inlineStr">
@@ -13179,7 +13691,7 @@
       </c>
       <c r="E28" s="102" t="inlineStr">
         <is>
-          <t>23/11/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="F28" s="136" t="inlineStr">
@@ -13204,19 +13716,19 @@
       </c>
       <c r="J28" s="93" t="inlineStr">
         <is>
-          <t>20 días. Ensayos de rutina + tipo en Brasil. AESA inspecciona (10 días de antelación)</t>
+          <t>★ HITO CLAVE: ÚLTIMO FREEZING POINT DE TODO EL PROYECTO ABB — 31-AGO-2026. Cierra toda la ingeniería. Sin hito en P6 ⚠</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="B29" s="102" t="inlineStr">
         <is>
-          <t>S3-13</t>
+          <t>S3-10</t>
         </is>
       </c>
       <c r="C29" s="132" t="inlineStr">
         <is>
-          <t>FAT Sala Eléctrica #3  ← FAT MÁS TARDÍO DE ABB</t>
+          <t>Ensayos Celdas y Tableros BT Sala #3</t>
         </is>
       </c>
       <c r="D29" s="104" t="inlineStr">
@@ -13226,7 +13738,7 @@
       </c>
       <c r="E29" s="102" t="inlineStr">
         <is>
-          <t>19/04/2027</t>
+          <t>23/11/2026</t>
         </is>
       </c>
       <c r="F29" s="136" t="inlineStr">
@@ -13251,19 +13763,19 @@
       </c>
       <c r="J29" s="93" t="inlineStr">
         <is>
-          <t>17 días. FAT integrado Shelter S#3 completo. P6 cierra FDE1103 el 24-MAY-2027. Holgura: 35 días</t>
+          <t>20 días. Ensayos de rutina + tipo en Brasil. AESA inspecciona (10 días de antelación)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="B30" s="102" t="inlineStr">
         <is>
-          <t>S3-14</t>
+          <t>S3-13</t>
         </is>
       </c>
       <c r="C30" s="132" t="inlineStr">
         <is>
-          <t>▶ DESPACHO Sala #3 ← DESPACHO MÁS TARDÍO DE ABB</t>
+          <t>FAT Sala Eléctrica #3  ← FAT MÁS TARDÍO DE ABB</t>
         </is>
       </c>
       <c r="D30" s="104" t="inlineStr">
@@ -13273,7 +13785,7 @@
       </c>
       <c r="E30" s="102" t="inlineStr">
         <is>
-          <t>14/05/2027</t>
+          <t>19/04/2027</t>
         </is>
       </c>
       <c r="F30" s="136" t="inlineStr">
@@ -13298,113 +13810,113 @@
       </c>
       <c r="J30" s="93" t="inlineStr">
         <is>
-          <t>ÚLTIMO DESPACHO ABB. OC deadline: 14-MAY-2027. P6 inicio montaje campo: 28-JUN-2027. Holgura: 45 días</t>
+          <t>17 días. FAT integrado Shelter S#3 completo. P6 cierra FDE1103 el 24-MAY-2027. Holgura: 35 días</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="B31" s="102" t="inlineStr">
         <is>
+          <t>S3-14</t>
+        </is>
+      </c>
+      <c r="C31" s="132" t="inlineStr">
+        <is>
+          <t>▶ DESPACHO Sala #3 ← DESPACHO MÁS TARDÍO DE ABB</t>
+        </is>
+      </c>
+      <c r="D31" s="104" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="E31" s="102" t="inlineStr">
+        <is>
+          <t>14/05/2027</t>
+        </is>
+      </c>
+      <c r="F31" s="136" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="137" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H31" s="138" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I31" s="136" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="93" t="inlineStr">
+        <is>
+          <t>ÚLTIMO DESPACHO ABB. OC deadline: 14-MAY-2027. P6 inicio montaje campo: 28-JUN-2027. Holgura: 45 días</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="102" t="inlineStr">
+        <is>
           <t>S3-15</t>
         </is>
       </c>
-      <c r="C31" s="132" t="inlineStr">
+      <c r="C32" s="132" t="inlineStr">
         <is>
           <t>★ ENTREGA S#3 — Cumplimiento OC 4508944971</t>
         </is>
       </c>
-      <c r="D31" s="104" t="inlineStr">
+      <c r="D32" s="104" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="E31" s="102" t="inlineStr">
+      <c r="E32" s="102" t="inlineStr">
         <is>
           <t>14/05/2027</t>
         </is>
       </c>
-      <c r="F31" s="136" t="inlineStr">
+      <c r="F32" s="136" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="137" t="inlineStr">
+      <c r="G32" s="137" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="H31" s="138" t="inlineStr">
+      <c r="H32" s="138" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I31" s="136" t="inlineStr">
+      <c r="I32" s="136" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J31" s="93" t="inlineStr">
+      <c r="J32" s="93" t="inlineStr">
         <is>
           <t>FECHA CONTRACTUAL: 14-MAY-2027 (12 meses). CADENA CRÍTICA — determina todo el cronograma ABB</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="149" t="inlineStr">
-        <is>
-          <t>PAY-01</t>
-        </is>
-      </c>
-      <c r="C32" s="150" t="inlineStr">
-        <is>
-          <t>§ 10% — Envío Ingeniería Básica (S3 + S4 + PMS)</t>
-        </is>
-      </c>
-      <c r="D32" s="151" t="inlineStr">
-        <is>
-          <t>S3+S4+PMS</t>
-        </is>
-      </c>
-      <c r="E32" s="152" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="F32" s="136" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="137" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H32" s="138" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="136" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J32" s="153" t="inlineStr">
-        <is>
-          <t>Emisión IB de los tres alcances. Póliza Caución Avance Fabricación requerida previamente</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="B33" s="149" t="inlineStr">
         <is>
-          <t>PAY-02</t>
+          <t>PAY-01</t>
         </is>
       </c>
       <c r="C33" s="150" t="inlineStr">
         <is>
-          <t>§ 10% — Aprobación Ingeniería Básica (AESA aprueba)</t>
+          <t>§ 10% — Envío Ingeniería Básica (S3 + S4 + PMS)</t>
         </is>
       </c>
       <c r="D33" s="151" t="inlineStr">
@@ -13414,7 +13926,7 @@
       </c>
       <c r="E33" s="152" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="F33" s="136" t="inlineStr">
@@ -13439,29 +13951,29 @@
       </c>
       <c r="J33" s="153" t="inlineStr">
         <is>
-          <t>Aprobación final IB por AESA. Póliza Caución Avance Fabricación vigente</t>
+          <t>Emisión IB de los tres alcances. Póliza Caución Avance Fabricación requerida previamente</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="B34" s="149" t="inlineStr">
         <is>
-          <t>PAY-03</t>
+          <t>PAY-02</t>
         </is>
       </c>
       <c r="C34" s="150" t="inlineStr">
         <is>
-          <t>§ 20% — FAT completado (S3 más tardío: 19-ABR-2027)</t>
+          <t>§ 10% — Aprobación Ingeniería Básica (AESA aprueba)</t>
         </is>
       </c>
       <c r="D34" s="151" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S3+S4+PMS</t>
         </is>
       </c>
       <c r="E34" s="152" t="inlineStr">
         <is>
-          <t>19/04/2027</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="F34" s="136" t="inlineStr">
@@ -13486,29 +13998,29 @@
       </c>
       <c r="J34" s="153" t="inlineStr">
         <is>
-          <t>FAT de integración S#3. Póliza Caución Avance Fabricación requerida. PMS: ver acuerdo FAT en Shelter</t>
+          <t>Aprobación final IB por AESA. Póliza Caución Avance Fabricación vigente</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="B35" s="149" t="inlineStr">
         <is>
-          <t>PAY-04</t>
+          <t>PAY-03</t>
         </is>
       </c>
       <c r="C35" s="150" t="inlineStr">
         <is>
-          <t>§ 25% — Acopio Materiales Principales en Argentina</t>
+          <t>§ 20% — FAT completado (S3 más tardío: 19-ABR-2027)</t>
         </is>
       </c>
       <c r="D35" s="151" t="inlineStr">
         <is>
-          <t>S3+S4+PMS</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="E35" s="152" t="inlineStr">
         <is>
-          <t>29/01/2027</t>
+          <t>19/04/2027</t>
         </is>
       </c>
       <c r="F35" s="136" t="inlineStr">
@@ -13533,19 +14045,19 @@
       </c>
       <c r="J35" s="153" t="inlineStr">
         <is>
-          <t>Celdas MT + tableros BT arco interno + ductos + VFDs MT/BT + PMS + UPS + aux. Póliza Caución Acopio</t>
+          <t>FAT de integración S#3. Póliza Caución Avance Fabricación requerida. PMS: ver acuerdo FAT en Shelter</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="B36" s="149" t="inlineStr">
         <is>
-          <t>PAY-05</t>
+          <t>PAY-04</t>
         </is>
       </c>
       <c r="C36" s="150" t="inlineStr">
         <is>
-          <t>§ 30% — Contra Entrega (Shelter listo en Mendoza)</t>
+          <t>§ 25% — Acopio Materiales Principales en Argentina</t>
         </is>
       </c>
       <c r="D36" s="151" t="inlineStr">
@@ -13555,7 +14067,7 @@
       </c>
       <c r="E36" s="152" t="inlineStr">
         <is>
-          <t>14/05/2027</t>
+          <t>29/01/2027</t>
         </is>
       </c>
       <c r="F36" s="136" t="inlineStr">
@@ -13580,153 +14092,200 @@
       </c>
       <c r="J36" s="153" t="inlineStr">
         <is>
-          <t>30 días desde Despacho S#3 (última entrega). Liberación por Calidad del COMPRADOR</t>
+          <t>Celdas MT + tableros BT arco interno + ductos + VFDs MT/BT + PMS + UPS + aux. Póliza Caución Acopio</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="B37" s="149" t="inlineStr">
         <is>
+          <t>PAY-05</t>
+        </is>
+      </c>
+      <c r="C37" s="150" t="inlineStr">
+        <is>
+          <t>§ 30% — Contra Entrega (Shelter listo en Mendoza)</t>
+        </is>
+      </c>
+      <c r="D37" s="151" t="inlineStr">
+        <is>
+          <t>S3+S4+PMS</t>
+        </is>
+      </c>
+      <c r="E37" s="152" t="inlineStr">
+        <is>
+          <t>14/05/2027</t>
+        </is>
+      </c>
+      <c r="F37" s="136" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="137" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H37" s="138" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I37" s="136" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J37" s="153" t="inlineStr">
+        <is>
+          <t>30 días desde Despacho S#3 (última entrega). Liberación por Calidad del COMPRADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="B38" s="149" t="inlineStr">
+        <is>
           <t>PAY-06</t>
         </is>
       </c>
-      <c r="C37" s="150" t="inlineStr">
+      <c r="C38" s="150" t="inlineStr">
         <is>
           <t>§ 5% — Entrega Databook aprobado</t>
         </is>
       </c>
-      <c r="D37" s="151" t="inlineStr">
+      <c r="D38" s="151" t="inlineStr">
         <is>
           <t>S3+S4+PMS</t>
         </is>
       </c>
-      <c r="E37" s="152" t="inlineStr">
+      <c r="E38" s="152" t="inlineStr">
         <is>
           <t>01/07/2027</t>
         </is>
       </c>
-      <c r="F37" s="136" t="inlineStr">
+      <c r="F38" s="136" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G37" s="137" t="inlineStr">
+      <c r="G38" s="137" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="H37" s="138" t="inlineStr">
+      <c r="H38" s="138" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I37" s="136" t="inlineStr">
+      <c r="I38" s="136" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J37" s="153" t="inlineStr">
+      <c r="J38" s="153" t="inlineStr">
         <is>
           <t>Databook completo y aprobado por AESA. Fecha estimada ~6-8 semanas post entrega</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="B38" s="102" t="inlineStr">
-        <is>
-          <t>INT-02</t>
-        </is>
-      </c>
-      <c r="C38" s="132" t="inlineStr">
-        <is>
-          <t>iFAT — Integración Shelters + PMS + INAUCO + HIMA</t>
-        </is>
-      </c>
-      <c r="D38" s="104" t="inlineStr">
-        <is>
-          <t>S3+S4+PMS</t>
-        </is>
-      </c>
-      <c r="E38" s="102" t="inlineStr">
-        <is>
-          <t>14/07/2027</t>
-        </is>
-      </c>
-      <c r="F38" s="136" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" s="137" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H38" s="138" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I38" s="136" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J38" s="93" t="inlineStr">
-        <is>
-          <t>P6: TA1124 = 28-JUN-2027. ABB arranca 25-JUN. Todos los vendors integran. Holgura: 3 días</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="B39" s="102" t="inlineStr">
         <is>
+          <t>INT-02</t>
+        </is>
+      </c>
+      <c r="C39" s="132" t="inlineStr">
+        <is>
+          <t>iFAT — Integración Shelters + PMS + INAUCO + HIMA</t>
+        </is>
+      </c>
+      <c r="D39" s="104" t="inlineStr">
+        <is>
+          <t>S3+S4+PMS</t>
+        </is>
+      </c>
+      <c r="E39" s="102" t="inlineStr">
+        <is>
+          <t>14/07/2027</t>
+        </is>
+      </c>
+      <c r="F39" s="136" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="137" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H39" s="138" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I39" s="136" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J39" s="93" t="inlineStr">
+        <is>
+          <t>P6: TA1124 = 28-JUN-2027. ABB arranca 25-JUN. Todos los vendors integran. Holgura: 3 días</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="B40" s="102" t="inlineStr">
+        <is>
           <t>INT-05</t>
         </is>
       </c>
-      <c r="C39" s="132" t="inlineStr">
+      <c r="C40" s="132" t="inlineStr">
         <is>
           <t>★ RFSU — Ready For Start Up Planta Total</t>
         </is>
       </c>
-      <c r="D39" s="104" t="inlineStr">
+      <c r="D40" s="104" t="inlineStr">
         <is>
           <t>PROYECTO</t>
         </is>
       </c>
-      <c r="E39" s="102" t="inlineStr">
+      <c r="E40" s="102" t="inlineStr">
         <is>
           <t>31/01/2028</t>
         </is>
       </c>
-      <c r="F39" s="136" t="inlineStr">
+      <c r="F40" s="136" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G39" s="137" t="inlineStr">
+      <c r="G40" s="137" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="H39" s="138" t="inlineStr">
+      <c r="H40" s="138" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I39" s="136" t="inlineStr">
+      <c r="I40" s="136" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J39" s="93" t="inlineStr">
+      <c r="J40" s="93" t="inlineStr">
         <is>
           <t>A10290. FECHA IDÉNTICA P6 y ABB ✅ Objetivo firme. Fin garantía extendida: 31-ENE-2029</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="B41" s="154" t="inlineStr">
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="154" t="inlineStr">
         <is>
           <t>INSTRUCCIONES: Fecha Real = fecha real de ocurrencia | Estado: Completado / Pendiente / En proceso / En riesgo | Desvío = Fecha Real - Fecha Plan (días)</t>
         </is>
@@ -13734,7 +14293,7 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B41:J41"/>
+    <mergeCell ref="B42:J42"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="B2:J2"/>
@@ -13749,7 +14308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H15"/>
+  <dimension ref="B1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -14206,6 +14765,80 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="50" customHeight="1">
+      <c r="B16" s="80" t="inlineStr">
+        <is>
+          <t>🟡 IMPORTANTE</t>
+        </is>
+      </c>
+      <c r="C16" s="160" t="inlineStr">
+        <is>
+          <t>AESA obligatorio en FAT Maqueta PMS — Sep/Oct 2026 — planificar viaje a Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D16" s="161" t="inlineStr">
+        <is>
+          <t>AESA (Equipo Técnico / TDJ-PLC)</t>
+        </is>
+      </c>
+      <c r="E16" s="162" t="inlineStr">
+        <is>
+          <t>AGO-2026 (con 4 semanas de anticipación)</t>
+        </is>
+      </c>
+      <c r="F16" s="163" t="inlineStr">
+        <is>
+          <t>La ET ACAL-00102-ET-E-0005 sec.20 establece participación obligatoria de AESA en Pruebas Tempranas (mock-up PMS+CCM+AC800M). Sin AESA presente no se certifica el resultado de la prueba</t>
+        </is>
+      </c>
+      <c r="G16" s="161" t="inlineStr">
+        <is>
+          <t>Planificar viaje a BsAs para SEP-OCT 2026. Confirmar disponibilidad con ABB (Pablo Kalis) al menos 4 semanas antes del inicio</t>
+        </is>
+      </c>
+      <c r="H16" s="137" t="inlineStr">
+        <is>
+          <t>Pendiente — planificar</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="50" customHeight="1">
+      <c r="B17" s="120" t="inlineStr">
+        <is>
+          <t>🟢 INFO</t>
+        </is>
+      </c>
+      <c r="C17" s="170" t="inlineStr">
+        <is>
+          <t>Protocolo PMS cambiado: Ethernet TCP/IP → Modbus TCP/IP (acuerdo Oct 2025)</t>
+        </is>
+      </c>
+      <c r="D17" s="171" t="inlineStr">
+        <is>
+          <t>AESA + ABB + INAUCO</t>
+        </is>
+      </c>
+      <c r="E17" s="172" t="inlineStr">
+        <is>
+          <t>Vigente desde Oct-2025</t>
+        </is>
+      </c>
+      <c r="F17" s="173" t="inlineStr">
+        <is>
+          <t>Acordado en reunión AESA-INAUCO-ABB del 02-OCT-2025. Incorporado en ET Rev.0 (25-NOV-2025) sec.23. Afecta diseño de red FP-P1 y comunicación PLC-PMS con SCADA de Procesos</t>
+        </is>
+      </c>
+      <c r="G17" s="171" t="inlineStr">
+        <is>
+          <t>Verificar que ABB refleja el cambio en la IB PMS (P-01). Confirmar protocolo definitivo en revisión FP-P1</t>
+        </is>
+      </c>
+      <c r="H17" s="134" t="inlineStr">
+        <is>
+          <t>Acordado ✅ — verificar en IB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:H1"/>
